--- a/compare/output/dscale_Elec_downscaled_SSP460.xlsx
+++ b/compare/output/dscale_Elec_downscaled_SSP460.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3953.122384</v>
+        <v>3953.125187</v>
       </c>
       <c r="F2" t="n">
-        <v>10018.414343</v>
+        <v>10018.433084</v>
       </c>
       <c r="G2" t="n">
-        <v>17784.440564</v>
+        <v>17784.511443</v>
       </c>
       <c r="H2" t="n">
-        <v>27123.122891</v>
+        <v>27123.362147</v>
       </c>
       <c r="I2" t="n">
-        <v>36747.941841</v>
+        <v>36748.8769</v>
       </c>
       <c r="J2" t="n">
         <v>4315.304484</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>339.233748</v>
+        <v>339.233901</v>
       </c>
       <c r="F3" t="n">
-        <v>746.484615</v>
+        <v>746.485542</v>
       </c>
       <c r="G3" t="n">
-        <v>1190.402196</v>
+        <v>1190.405432</v>
       </c>
       <c r="H3" t="n">
-        <v>1694.76015</v>
+        <v>1694.770681</v>
       </c>
       <c r="I3" t="n">
-        <v>2224.08972</v>
+        <v>2224.130638</v>
       </c>
       <c r="J3" t="n">
         <v>1000.55127</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>394.513156</v>
+        <v>394.512743</v>
       </c>
       <c r="F4" t="n">
-        <v>807.03395</v>
+        <v>807.032046</v>
       </c>
       <c r="G4" t="n">
-        <v>1161.385829</v>
+        <v>1161.381059</v>
       </c>
       <c r="H4" t="n">
-        <v>1533.747213</v>
+        <v>1533.735687</v>
       </c>
       <c r="I4" t="n">
-        <v>1916.756185</v>
+        <v>1916.719906</v>
       </c>
       <c r="J4" t="n">
         <v>4064.356389</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1043.988636</v>
+        <v>1043.989042</v>
       </c>
       <c r="F5" t="n">
-        <v>3118.202138</v>
+        <v>3118.204377</v>
       </c>
       <c r="G5" t="n">
-        <v>6949.587515</v>
+        <v>6949.59049</v>
       </c>
       <c r="H5" t="n">
-        <v>12659.362427</v>
+        <v>12659.347194</v>
       </c>
       <c r="I5" t="n">
-        <v>19474.848675</v>
+        <v>19474.700038</v>
       </c>
       <c r="J5" t="n">
         <v>39022.465768</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38163.983855</v>
+        <v>38164.001322</v>
       </c>
       <c r="F6" t="n">
-        <v>96317.665041</v>
+        <v>96317.773871</v>
       </c>
       <c r="G6" t="n">
-        <v>156667.716342</v>
+        <v>156668.100921</v>
       </c>
       <c r="H6" t="n">
-        <v>223502.746041</v>
+        <v>223504.011087</v>
       </c>
       <c r="I6" t="n">
-        <v>295169.017461</v>
+        <v>295173.971839</v>
       </c>
       <c r="J6" t="n">
         <v>155539.835712</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>35543.069784</v>
+        <v>35543.082744</v>
       </c>
       <c r="F7" t="n">
-        <v>92581.361667</v>
+        <v>92581.43765000001</v>
       </c>
       <c r="G7" t="n">
-        <v>174124.277971</v>
+        <v>174124.512496</v>
       </c>
       <c r="H7" t="n">
-        <v>284751.038977</v>
+        <v>284751.682857</v>
       </c>
       <c r="I7" t="n">
-        <v>418030.301496</v>
+        <v>418032.316221</v>
       </c>
       <c r="J7" t="n">
         <v>540600.376725</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7724.054636</v>
+        <v>7724.058116</v>
       </c>
       <c r="F8" t="n">
-        <v>19899.591631</v>
+        <v>19899.613757</v>
       </c>
       <c r="G8" t="n">
-        <v>36561.002022</v>
+        <v>36561.081887</v>
       </c>
       <c r="H8" t="n">
-        <v>58361.495196</v>
+        <v>58361.762221</v>
       </c>
       <c r="I8" t="n">
-        <v>83574.58189</v>
+        <v>83575.64539600001</v>
       </c>
       <c r="J8" t="n">
         <v>66510.014736</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10940.037122</v>
+        <v>10940.017324</v>
       </c>
       <c r="F9" t="n">
-        <v>21606.390567</v>
+        <v>21606.295831</v>
       </c>
       <c r="G9" t="n">
-        <v>29352.916404</v>
+        <v>29352.680859</v>
       </c>
       <c r="H9" t="n">
-        <v>36037.243403</v>
+        <v>36036.702031</v>
       </c>
       <c r="I9" t="n">
-        <v>41785.482327</v>
+        <v>41783.907494</v>
       </c>
       <c r="J9" t="n">
         <v>114605.73847</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1923.717991</v>
+        <v>1923.716815</v>
       </c>
       <c r="F10" t="n">
-        <v>4363.130083</v>
+        <v>4363.123575</v>
       </c>
       <c r="G10" t="n">
-        <v>6725.560832</v>
+        <v>6725.543348</v>
       </c>
       <c r="H10" t="n">
-        <v>9442.877246</v>
+        <v>9442.833263</v>
       </c>
       <c r="I10" t="n">
-        <v>12352.572485</v>
+        <v>12352.437126</v>
       </c>
       <c r="J10" t="n">
         <v>22396.434031</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47676.785748</v>
+        <v>47676.768027</v>
       </c>
       <c r="F11" t="n">
-        <v>116048.796637</v>
+        <v>116048.659361</v>
       </c>
       <c r="G11" t="n">
-        <v>198728.349942</v>
+        <v>198727.77917</v>
       </c>
       <c r="H11" t="n">
-        <v>300938.922168</v>
+        <v>300936.889777</v>
       </c>
       <c r="I11" t="n">
-        <v>411486.269953</v>
+        <v>411478.165549</v>
       </c>
       <c r="J11" t="n">
         <v>947144.0399870001</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4253.350917</v>
+        <v>4253.35379</v>
       </c>
       <c r="F12" t="n">
-        <v>10907.3507</v>
+        <v>10907.369934</v>
       </c>
       <c r="G12" t="n">
-        <v>20015.463855</v>
+        <v>20015.538137</v>
       </c>
       <c r="H12" t="n">
-        <v>32182.788827</v>
+        <v>32183.050276</v>
       </c>
       <c r="I12" t="n">
-        <v>46058.83737</v>
+        <v>46059.907497</v>
       </c>
       <c r="J12" t="n">
         <v>11482.75717</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13064.474024</v>
+        <v>13064.47299</v>
       </c>
       <c r="F13" t="n">
-        <v>32086.850328</v>
+        <v>32086.842671</v>
       </c>
       <c r="G13" t="n">
-        <v>54458.933728</v>
+        <v>54458.911958</v>
       </c>
       <c r="H13" t="n">
-        <v>82902.86546</v>
+        <v>82902.82277899999</v>
       </c>
       <c r="I13" t="n">
-        <v>116846.137898</v>
+        <v>116846.058698</v>
       </c>
       <c r="J13" t="n">
         <v>170701.185558</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>246593.97448</v>
+        <v>246588.133083</v>
       </c>
       <c r="F14" t="n">
-        <v>310634.160711</v>
+        <v>310614.284005</v>
       </c>
       <c r="G14" t="n">
-        <v>403375.608676</v>
+        <v>403322.552192</v>
       </c>
       <c r="H14" t="n">
-        <v>516757.400501</v>
+        <v>516622.001867</v>
       </c>
       <c r="I14" t="n">
-        <v>642715.430298</v>
+        <v>642312.66624</v>
       </c>
       <c r="J14" t="n">
         <v>875117.749342</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>667074.764213</v>
+        <v>667090.403298</v>
       </c>
       <c r="F15" t="n">
-        <v>927648.733501</v>
+        <v>927702.884925</v>
       </c>
       <c r="G15" t="n">
-        <v>1262772.461892</v>
+        <v>1262917.771324</v>
       </c>
       <c r="H15" t="n">
-        <v>1647280.549135</v>
+        <v>1647649.188215</v>
       </c>
       <c r="I15" t="n">
-        <v>2045946.91894</v>
+        <v>2047032.450934</v>
       </c>
       <c r="J15" t="n">
         <v>2154979.285146</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>134419.141343</v>
+        <v>134420.688016</v>
       </c>
       <c r="F16" t="n">
-        <v>149120.517248</v>
+        <v>149122.765995</v>
       </c>
       <c r="G16" t="n">
-        <v>165122.347826</v>
+        <v>165123.069551</v>
       </c>
       <c r="H16" t="n">
-        <v>186679.73747</v>
+        <v>186674.454513</v>
       </c>
       <c r="I16" t="n">
-        <v>212615.292385</v>
+        <v>212588.172403</v>
       </c>
       <c r="J16" t="n">
         <v>249768.13075</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>110498.119804</v>
+        <v>110490.661724</v>
       </c>
       <c r="F17" t="n">
-        <v>138481.231501</v>
+        <v>138457.541954</v>
       </c>
       <c r="G17" t="n">
-        <v>173004.060219</v>
+        <v>172944.206081</v>
       </c>
       <c r="H17" t="n">
-        <v>210707.476355</v>
+        <v>210561.722264</v>
       </c>
       <c r="I17" t="n">
-        <v>248056.059243</v>
+        <v>247640.60528</v>
       </c>
       <c r="J17" t="n">
         <v>382078.631346</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>70522.040095</v>
+        <v>70518.153813</v>
       </c>
       <c r="F18" t="n">
-        <v>95812.812299</v>
+        <v>95799.978382</v>
       </c>
       <c r="G18" t="n">
-        <v>123633.532588</v>
+        <v>123600.412051</v>
       </c>
       <c r="H18" t="n">
-        <v>154821.88334</v>
+        <v>154739.67994</v>
       </c>
       <c r="I18" t="n">
-        <v>190076.265934</v>
+        <v>189836.071942</v>
       </c>
       <c r="J18" t="n">
         <v>292034.012216</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>36544.916663</v>
+        <v>36544.761429</v>
       </c>
       <c r="F19" t="n">
-        <v>61597.617647</v>
+        <v>61596.926196</v>
       </c>
       <c r="G19" t="n">
-        <v>82647.193764</v>
+        <v>82645.27858499999</v>
       </c>
       <c r="H19" t="n">
-        <v>111238.554167</v>
+        <v>111233.217766</v>
       </c>
       <c r="I19" t="n">
-        <v>144906.117333</v>
+        <v>144887.948752</v>
       </c>
       <c r="J19" t="n">
         <v>586185.963142</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10652.08295</v>
+        <v>10652.029319</v>
       </c>
       <c r="F20" t="n">
-        <v>17337.375943</v>
+        <v>17337.127783</v>
       </c>
       <c r="G20" t="n">
-        <v>23381.625657</v>
+        <v>23380.85125</v>
       </c>
       <c r="H20" t="n">
-        <v>30811.172376</v>
+        <v>30808.874156</v>
       </c>
       <c r="I20" t="n">
-        <v>38365.643013</v>
+        <v>38357.771756</v>
       </c>
       <c r="J20" t="n">
         <v>213845.188676</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>954.7305720000001</v>
+        <v>954.729859</v>
       </c>
       <c r="F21" t="n">
-        <v>1281.632084</v>
+        <v>1281.630337</v>
       </c>
       <c r="G21" t="n">
-        <v>1436.405205</v>
+        <v>1436.402196</v>
       </c>
       <c r="H21" t="n">
-        <v>1710.393333</v>
+        <v>1710.386511</v>
       </c>
       <c r="I21" t="n">
-        <v>2053.3483</v>
+        <v>2053.324406</v>
       </c>
       <c r="J21" t="n">
         <v>3021.494737</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69646.023783</v>
+        <v>69646.14240300001</v>
       </c>
       <c r="F22" t="n">
-        <v>118796.023705</v>
+        <v>118796.564772</v>
       </c>
       <c r="G22" t="n">
-        <v>159676.482226</v>
+        <v>159677.993457</v>
       </c>
       <c r="H22" t="n">
-        <v>213499.861607</v>
+        <v>213504.005157</v>
       </c>
       <c r="I22" t="n">
-        <v>274787.831025</v>
+        <v>274801.400824</v>
       </c>
       <c r="J22" t="n">
         <v>51315.897011</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7312.386196</v>
+        <v>7312.39264</v>
       </c>
       <c r="F23" t="n">
-        <v>13302.929727</v>
+        <v>13302.959825</v>
       </c>
       <c r="G23" t="n">
-        <v>19516.505221</v>
+        <v>19516.591601</v>
       </c>
       <c r="H23" t="n">
-        <v>28987.274133</v>
+        <v>28987.515851</v>
       </c>
       <c r="I23" t="n">
-        <v>41712.099342</v>
+        <v>41712.891367</v>
       </c>
       <c r="J23" t="n">
         <v>40958.461108</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5829.99769</v>
+        <v>5829.979944</v>
       </c>
       <c r="F24" t="n">
-        <v>9255.335126</v>
+        <v>9255.259509</v>
       </c>
       <c r="G24" t="n">
-        <v>12092.883339</v>
+        <v>12092.668243</v>
       </c>
       <c r="H24" t="n">
-        <v>15841.399617</v>
+        <v>15840.788452</v>
       </c>
       <c r="I24" t="n">
-        <v>20061.82679</v>
+        <v>20059.722387</v>
       </c>
       <c r="J24" t="n">
         <v>71119.345568</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1429.293345</v>
+        <v>1429.288321</v>
       </c>
       <c r="F25" t="n">
-        <v>2034.029151</v>
+        <v>2034.011684</v>
       </c>
       <c r="G25" t="n">
-        <v>2415.238954</v>
+        <v>2415.197102</v>
       </c>
       <c r="H25" t="n">
-        <v>2992.697661</v>
+        <v>2992.588723</v>
       </c>
       <c r="I25" t="n">
-        <v>3676.06899</v>
+        <v>3675.70818</v>
       </c>
       <c r="J25" t="n">
         <v>12190.854634</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>24591.003494</v>
+        <v>24590.985488</v>
       </c>
       <c r="F26" t="n">
-        <v>39900.914554</v>
+        <v>39900.84549</v>
       </c>
       <c r="G26" t="n">
-        <v>50668.254109</v>
+        <v>50668.099734</v>
       </c>
       <c r="H26" t="n">
-        <v>65590.937553</v>
+        <v>65590.56686200001</v>
       </c>
       <c r="I26" t="n">
-        <v>83251.078454</v>
+        <v>83249.905121</v>
       </c>
       <c r="J26" t="n">
         <v>128443.756528</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>50795.094371</v>
+        <v>50795.148334</v>
       </c>
       <c r="F27" t="n">
-        <v>84586.40925700001</v>
+        <v>84586.65541799999</v>
       </c>
       <c r="G27" t="n">
-        <v>109294.03804</v>
+        <v>109294.718886</v>
       </c>
       <c r="H27" t="n">
-        <v>143608.190372</v>
+        <v>143610.055661</v>
       </c>
       <c r="I27" t="n">
-        <v>186207.337431</v>
+        <v>186213.508961</v>
       </c>
       <c r="J27" t="n">
         <v>101960.468757</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>36525.915237</v>
+        <v>36525.986563</v>
       </c>
       <c r="F28" t="n">
-        <v>54577.565501</v>
+        <v>54577.851681</v>
       </c>
       <c r="G28" t="n">
-        <v>75505.801594</v>
+        <v>75506.627056</v>
       </c>
       <c r="H28" t="n">
-        <v>110348.455881</v>
+        <v>110350.93756</v>
       </c>
       <c r="I28" t="n">
-        <v>159590.303323</v>
+        <v>159599.472247</v>
       </c>
       <c r="J28" t="n">
         <v>1663.677538</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1001.060114</v>
+        <v>1001.059989</v>
       </c>
       <c r="F29" t="n">
-        <v>1518.152273</v>
+        <v>1518.151807</v>
       </c>
       <c r="G29" t="n">
-        <v>2131.947029</v>
+        <v>2131.94557</v>
       </c>
       <c r="H29" t="n">
-        <v>2980.673246</v>
+        <v>2980.668675</v>
       </c>
       <c r="I29" t="n">
-        <v>3955.880777</v>
+        <v>3955.864081</v>
       </c>
       <c r="J29" t="n">
         <v>10391.393028</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5739.401078</v>
+        <v>5739.401609</v>
       </c>
       <c r="F30" t="n">
-        <v>7044.978918</v>
+        <v>7044.980891</v>
       </c>
       <c r="G30" t="n">
-        <v>8020.038141</v>
+        <v>8020.043008</v>
       </c>
       <c r="H30" t="n">
-        <v>9965.840217999999</v>
+        <v>9965.852916</v>
       </c>
       <c r="I30" t="n">
-        <v>12667.667039</v>
+        <v>12667.709857</v>
       </c>
       <c r="J30" t="n">
         <v>3024.120816</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1641.415145</v>
+        <v>1641.415325</v>
       </c>
       <c r="F31" t="n">
-        <v>2397.649055</v>
+        <v>2397.649778</v>
       </c>
       <c r="G31" t="n">
-        <v>3107.586652</v>
+        <v>3107.588578</v>
       </c>
       <c r="H31" t="n">
-        <v>4095.926827</v>
+        <v>4095.932011</v>
       </c>
       <c r="I31" t="n">
-        <v>5192.35906</v>
+        <v>5192.376291</v>
       </c>
       <c r="J31" t="n">
         <v>1297.238222</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>26424.902385</v>
+        <v>26424.905314</v>
       </c>
       <c r="F32" t="n">
-        <v>35444.820768</v>
+        <v>35444.831772</v>
       </c>
       <c r="G32" t="n">
-        <v>43913.721018</v>
+        <v>43913.749301</v>
       </c>
       <c r="H32" t="n">
-        <v>56457.208199</v>
+        <v>56457.282948</v>
       </c>
       <c r="I32" t="n">
-        <v>71392.275655</v>
+        <v>71392.523906</v>
       </c>
       <c r="J32" t="n">
         <v>14701.668688</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>24192.24615</v>
+        <v>24192.247996</v>
       </c>
       <c r="F33" t="n">
-        <v>35348.782005</v>
+        <v>35348.789645</v>
       </c>
       <c r="G33" t="n">
-        <v>47514.952259</v>
+        <v>47514.97294</v>
       </c>
       <c r="H33" t="n">
-        <v>64165.242241</v>
+        <v>64165.29787</v>
       </c>
       <c r="I33" t="n">
-        <v>82724.56527000001</v>
+        <v>82724.75045599999</v>
       </c>
       <c r="J33" t="n">
         <v>47957.23758</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27165.074987</v>
+        <v>27165.078455</v>
       </c>
       <c r="F34" t="n">
-        <v>70009.405141</v>
+        <v>70009.428369</v>
       </c>
       <c r="G34" t="n">
-        <v>159512.18365</v>
+        <v>159512.283395</v>
       </c>
       <c r="H34" t="n">
-        <v>310575.255596</v>
+        <v>310575.615414</v>
       </c>
       <c r="I34" t="n">
-        <v>506534.518637</v>
+        <v>506535.925737</v>
       </c>
       <c r="J34" t="n">
         <v>272291.651596</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8399.79126</v>
+        <v>8399.791814</v>
       </c>
       <c r="F35" t="n">
-        <v>15296.390414</v>
+        <v>15296.392709</v>
       </c>
       <c r="G35" t="n">
-        <v>25105.402749</v>
+        <v>25105.407946</v>
       </c>
       <c r="H35" t="n">
-        <v>38194.171622</v>
+        <v>38194.18151</v>
       </c>
       <c r="I35" t="n">
-        <v>51889.624581</v>
+        <v>51889.649605</v>
       </c>
       <c r="J35" t="n">
         <v>58168.031707</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>174.005879</v>
+        <v>174.005682</v>
       </c>
       <c r="F36" t="n">
-        <v>258.138868</v>
+        <v>258.138042</v>
       </c>
       <c r="G36" t="n">
-        <v>311.263835</v>
+        <v>311.261802</v>
       </c>
       <c r="H36" t="n">
-        <v>362.401976</v>
+        <v>362.397273</v>
       </c>
       <c r="I36" t="n">
-        <v>403.385017</v>
+        <v>403.371987</v>
       </c>
       <c r="J36" t="n">
         <v>3754.476177</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7325.947429</v>
+        <v>7325.945599</v>
       </c>
       <c r="F37" t="n">
-        <v>9471.427006</v>
+        <v>9471.421958999999</v>
       </c>
       <c r="G37" t="n">
-        <v>11226.942889</v>
+        <v>11226.932141</v>
       </c>
       <c r="H37" t="n">
-        <v>13680.915532</v>
+        <v>13680.890618</v>
       </c>
       <c r="I37" t="n">
-        <v>16289.974255</v>
+        <v>16289.901362</v>
       </c>
       <c r="J37" t="n">
         <v>38405.796293</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>35067.372519</v>
+        <v>35067.37626</v>
       </c>
       <c r="F38" t="n">
-        <v>53593.20092</v>
+        <v>53593.216568</v>
       </c>
       <c r="G38" t="n">
-        <v>71912.398995</v>
+        <v>71912.442006</v>
       </c>
       <c r="H38" t="n">
-        <v>97177.79942</v>
+        <v>97177.918034</v>
       </c>
       <c r="I38" t="n">
-        <v>127224.119195</v>
+        <v>127224.525436</v>
       </c>
       <c r="J38" t="n">
         <v>38601.335325</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3728.771602</v>
+        <v>3728.77197</v>
       </c>
       <c r="F39" t="n">
-        <v>5018.037979</v>
+        <v>5018.039386</v>
       </c>
       <c r="G39" t="n">
-        <v>6339.173152</v>
+        <v>6339.176832</v>
       </c>
       <c r="H39" t="n">
-        <v>8264.678878999999</v>
+        <v>8264.688689000001</v>
       </c>
       <c r="I39" t="n">
-        <v>10483.09407</v>
+        <v>10483.126612</v>
       </c>
       <c r="J39" t="n">
         <v>3330.372851</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>568.323198</v>
+        <v>568.3232420000001</v>
       </c>
       <c r="F40" t="n">
-        <v>838.266171</v>
+        <v>838.266353</v>
       </c>
       <c r="G40" t="n">
-        <v>1116.316314</v>
+        <v>1116.316803</v>
       </c>
       <c r="H40" t="n">
-        <v>1468.257033</v>
+        <v>1468.258335</v>
       </c>
       <c r="I40" t="n">
-        <v>1854.423168</v>
+        <v>1854.427463</v>
       </c>
       <c r="J40" t="n">
         <v>998.115606</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>669.076522</v>
+        <v>669.076474</v>
       </c>
       <c r="F41" t="n">
-        <v>1103.508104</v>
+        <v>1103.507858</v>
       </c>
       <c r="G41" t="n">
-        <v>1531.749919</v>
+        <v>1531.749143</v>
       </c>
       <c r="H41" t="n">
-        <v>2071.373377</v>
+        <v>2071.371093</v>
       </c>
       <c r="I41" t="n">
-        <v>2647.221598</v>
+        <v>2647.213939</v>
       </c>
       <c r="J41" t="n">
         <v>5492.977231</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3940.589527</v>
+        <v>3940.582588</v>
       </c>
       <c r="F42" t="n">
-        <v>5631.114555</v>
+        <v>5631.090314</v>
       </c>
       <c r="G42" t="n">
-        <v>7338.307461</v>
+        <v>7338.244542</v>
       </c>
       <c r="H42" t="n">
-        <v>9572.97841</v>
+        <v>9572.813013999999</v>
       </c>
       <c r="I42" t="n">
-        <v>11964.635626</v>
+        <v>11964.107584</v>
       </c>
       <c r="J42" t="n">
         <v>165334.110444</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1654.588469</v>
+        <v>1654.588676</v>
       </c>
       <c r="F43" t="n">
-        <v>3292.386111</v>
+        <v>3292.387208</v>
       </c>
       <c r="G43" t="n">
-        <v>5676.739452</v>
+        <v>5676.743229</v>
       </c>
       <c r="H43" t="n">
-        <v>9268.891054</v>
+        <v>9268.903366</v>
       </c>
       <c r="I43" t="n">
-        <v>13753.556761</v>
+        <v>13753.603774</v>
       </c>
       <c r="J43" t="n">
         <v>3612.994762</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7732.417924</v>
+        <v>7732.418552</v>
       </c>
       <c r="F44" t="n">
-        <v>12297.699943</v>
+        <v>12297.702692</v>
       </c>
       <c r="G44" t="n">
-        <v>17656.703614</v>
+        <v>17656.711474</v>
       </c>
       <c r="H44" t="n">
-        <v>25440.600064</v>
+        <v>25440.622355</v>
       </c>
       <c r="I44" t="n">
-        <v>34837.063245</v>
+        <v>34837.141048</v>
       </c>
       <c r="J44" t="n">
         <v>21760.587512</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4607.902241</v>
+        <v>4607.902616</v>
       </c>
       <c r="F45" t="n">
-        <v>7389.027606</v>
+        <v>7389.029211</v>
       </c>
       <c r="G45" t="n">
-        <v>10385.05164</v>
+        <v>10385.056076</v>
       </c>
       <c r="H45" t="n">
-        <v>14245.188437</v>
+        <v>14245.200508</v>
       </c>
       <c r="I45" t="n">
-        <v>18484.344574</v>
+        <v>18484.385138</v>
       </c>
       <c r="J45" t="n">
         <v>11067.962999</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1610.794213</v>
+        <v>1610.794319</v>
       </c>
       <c r="F46" t="n">
-        <v>2517.554142</v>
+        <v>2517.554623</v>
       </c>
       <c r="G46" t="n">
-        <v>3681.353574</v>
+        <v>3681.354995</v>
       </c>
       <c r="H46" t="n">
-        <v>5532.933314</v>
+        <v>5532.937496</v>
       </c>
       <c r="I46" t="n">
-        <v>8324.643459000001</v>
+        <v>8324.658664</v>
       </c>
       <c r="J46" t="n">
         <v>7539.866505</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>136559.681942</v>
+        <v>136559.675269</v>
       </c>
       <c r="F47" t="n">
-        <v>238463.723748</v>
+        <v>238463.680661</v>
       </c>
       <c r="G47" t="n">
-        <v>349302.403835</v>
+        <v>349302.245419</v>
       </c>
       <c r="H47" t="n">
-        <v>500255.205307</v>
+        <v>500254.678256</v>
       </c>
       <c r="I47" t="n">
-        <v>683193.002197</v>
+        <v>683190.9875169999</v>
       </c>
       <c r="J47" t="n">
         <v>1591711.876809</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12592.101289</v>
+        <v>12592.102341</v>
       </c>
       <c r="F48" t="n">
-        <v>18953.652009</v>
+        <v>18953.656466</v>
       </c>
       <c r="G48" t="n">
-        <v>25806.474206</v>
+        <v>25806.486621</v>
       </c>
       <c r="H48" t="n">
-        <v>34857.19355</v>
+        <v>34857.22784</v>
       </c>
       <c r="I48" t="n">
-        <v>44634.769867</v>
+        <v>44634.886357</v>
       </c>
       <c r="J48" t="n">
         <v>20030.856201</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2244.070627</v>
+        <v>2244.070778</v>
       </c>
       <c r="F49" t="n">
-        <v>3579.471101</v>
+        <v>3579.471739</v>
       </c>
       <c r="G49" t="n">
-        <v>4961.115791</v>
+        <v>4961.117518</v>
       </c>
       <c r="H49" t="n">
-        <v>6703.163104</v>
+        <v>6703.167741</v>
       </c>
       <c r="I49" t="n">
-        <v>8517.137839999999</v>
+        <v>8517.153399000001</v>
       </c>
       <c r="J49" t="n">
         <v>5793.277253</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>59.919243</v>
+        <v>59.919236</v>
       </c>
       <c r="F50" t="n">
-        <v>89.515411</v>
+        <v>89.515383</v>
       </c>
       <c r="G50" t="n">
-        <v>113.823532</v>
+        <v>113.823458</v>
       </c>
       <c r="H50" t="n">
-        <v>141.534863</v>
+        <v>141.534676</v>
       </c>
       <c r="I50" t="n">
-        <v>167.638794</v>
+        <v>167.638248</v>
       </c>
       <c r="J50" t="n">
         <v>339.746485</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>879.722045</v>
+        <v>879.721624</v>
       </c>
       <c r="F51" t="n">
-        <v>1258.795184</v>
+        <v>1258.793747</v>
       </c>
       <c r="G51" t="n">
-        <v>1656.190733</v>
+        <v>1656.186993</v>
       </c>
       <c r="H51" t="n">
-        <v>2204.945426</v>
+        <v>2204.935346</v>
       </c>
       <c r="I51" t="n">
-        <v>2834.057632</v>
+        <v>2834.024252</v>
       </c>
       <c r="J51" t="n">
         <v>13535.039274</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>910.05321</v>
+        <v>910.053272</v>
       </c>
       <c r="F52" t="n">
-        <v>1179.613469</v>
+        <v>1179.61372</v>
       </c>
       <c r="G52" t="n">
-        <v>1415.728207</v>
+        <v>1415.72886</v>
       </c>
       <c r="H52" t="n">
-        <v>1766.957805</v>
+        <v>1766.959517</v>
       </c>
       <c r="I52" t="n">
-        <v>2172.816683</v>
+        <v>2172.822285</v>
       </c>
       <c r="J52" t="n">
         <v>1003.850036</v>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>873047.472527</v>
+        <v>873039.7448559999</v>
       </c>
       <c r="F54" t="n">
-        <v>948092.536125</v>
+        <v>948076.571525</v>
       </c>
       <c r="G54" t="n">
-        <v>1121359.95678</v>
+        <v>1121330.253842</v>
       </c>
       <c r="H54" t="n">
-        <v>1313330.910164</v>
+        <v>1313274.282595</v>
       </c>
       <c r="I54" t="n">
-        <v>1500422.711485</v>
+        <v>1500294.442932</v>
       </c>
       <c r="J54" t="n">
         <v>1703894.777966</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>154939.553073</v>
+        <v>154947.280744</v>
       </c>
       <c r="F55" t="n">
-        <v>156218.350425</v>
+        <v>156234.315025</v>
       </c>
       <c r="G55" t="n">
-        <v>174079.28522</v>
+        <v>174108.988158</v>
       </c>
       <c r="H55" t="n">
-        <v>194528.028236</v>
+        <v>194584.655805</v>
       </c>
       <c r="I55" t="n">
-        <v>213558.654115</v>
+        <v>213686.922668</v>
       </c>
       <c r="J55" t="n">
         <v>214557.642634</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>19741.061925</v>
+        <v>19741.120812</v>
       </c>
       <c r="F58" t="n">
-        <v>26472.689852</v>
+        <v>26472.899761</v>
       </c>
       <c r="G58" t="n">
-        <v>35856.216159</v>
+        <v>35856.788326</v>
       </c>
       <c r="H58" t="n">
-        <v>46284.67052</v>
+        <v>46286.143917</v>
       </c>
       <c r="I58" t="n">
-        <v>58444.241</v>
+        <v>58448.863399</v>
       </c>
       <c r="J58" t="n">
         <v>41093.400394</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>18513.037687</v>
+        <v>18513.149932</v>
       </c>
       <c r="F59" t="n">
-        <v>25836.663629</v>
+        <v>25837.070895</v>
       </c>
       <c r="G59" t="n">
-        <v>36254.96036</v>
+        <v>36256.122105</v>
       </c>
       <c r="H59" t="n">
-        <v>47428.533741</v>
+        <v>47431.619952</v>
       </c>
       <c r="I59" t="n">
-        <v>60159.33376</v>
+        <v>60169.256601</v>
       </c>
       <c r="J59" t="n">
         <v>7193.9133</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>14912.613099</v>
+        <v>14912.679204</v>
       </c>
       <c r="F60" t="n">
-        <v>16436.112603</v>
+        <v>16436.309771</v>
       </c>
       <c r="G60" t="n">
-        <v>18304.246591</v>
+        <v>18304.705212</v>
       </c>
       <c r="H60" t="n">
-        <v>20440.194806</v>
+        <v>20441.249359</v>
       </c>
       <c r="I60" t="n">
-        <v>23419.246347</v>
+        <v>23422.322404</v>
       </c>
       <c r="J60" t="n">
         <v>7587.546488</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38923.303186</v>
+        <v>38923.289022</v>
       </c>
       <c r="F61" t="n">
-        <v>52048.539479</v>
+        <v>52048.513543</v>
       </c>
       <c r="G61" t="n">
-        <v>66939.07589599999</v>
+        <v>66939.050531</v>
       </c>
       <c r="H61" t="n">
-        <v>81541.852445</v>
+        <v>81541.874751</v>
       </c>
       <c r="I61" t="n">
-        <v>97809.703908</v>
+        <v>97809.95524700001</v>
       </c>
       <c r="J61" t="n">
         <v>113221.356669</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>73038.78454199999</v>
+        <v>73038.51214000001</v>
       </c>
       <c r="F62" t="n">
-        <v>104345.410524</v>
+        <v>104344.289488</v>
       </c>
       <c r="G62" t="n">
-        <v>139273.672731</v>
+        <v>139270.377906</v>
       </c>
       <c r="H62" t="n">
-        <v>170263.326093</v>
+        <v>170254.776763</v>
       </c>
       <c r="I62" t="n">
-        <v>199844.70448</v>
+        <v>199818.658552</v>
       </c>
       <c r="J62" t="n">
         <v>390140.657029</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>64786.364683</v>
+        <v>64786.259722</v>
       </c>
       <c r="F63" t="n">
-        <v>89905.119317</v>
+        <v>89904.74339</v>
       </c>
       <c r="G63" t="n">
-        <v>115830.889909</v>
+        <v>115829.956254</v>
       </c>
       <c r="H63" t="n">
-        <v>140748.736487</v>
+        <v>140746.543025</v>
       </c>
       <c r="I63" t="n">
-        <v>169488.849771</v>
+        <v>169482.228465</v>
       </c>
       <c r="J63" t="n">
         <v>247750.900652</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5691.395115</v>
+        <v>5691.427582</v>
       </c>
       <c r="F64" t="n">
-        <v>6934.069165</v>
+        <v>6934.172528</v>
       </c>
       <c r="G64" t="n">
-        <v>8543.447620999999</v>
+        <v>8543.707318000001</v>
       </c>
       <c r="H64" t="n">
-        <v>10160.930467</v>
+        <v>10161.558377</v>
       </c>
       <c r="I64" t="n">
-        <v>12038.384382</v>
+        <v>12040.269583</v>
       </c>
       <c r="J64" t="n">
         <v>2019.513489</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>42091.398885</v>
+        <v>42091.305865</v>
       </c>
       <c r="F65" t="n">
-        <v>61084.938631</v>
+        <v>61084.606175</v>
       </c>
       <c r="G65" t="n">
-        <v>86719.962325</v>
+        <v>86719.00133100001</v>
       </c>
       <c r="H65" t="n">
-        <v>116722.881848</v>
+        <v>116720.227015</v>
       </c>
       <c r="I65" t="n">
-        <v>154026.5999</v>
+        <v>154017.512289</v>
       </c>
       <c r="J65" t="n">
         <v>264219.673952</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>32568.259497</v>
+        <v>32568.388592</v>
       </c>
       <c r="F66" t="n">
-        <v>46116.830771</v>
+        <v>46117.309729</v>
       </c>
       <c r="G66" t="n">
-        <v>63935.300658</v>
+        <v>63936.652043</v>
       </c>
       <c r="H66" t="n">
-        <v>84053.038709</v>
+        <v>84056.642146</v>
       </c>
       <c r="I66" t="n">
-        <v>108366.08936</v>
+        <v>108377.822584</v>
       </c>
       <c r="J66" t="n">
         <v>55913.299211</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3740.428502</v>
+        <v>3740.42459</v>
       </c>
       <c r="F67" t="n">
-        <v>5417.643956</v>
+        <v>5417.627739</v>
       </c>
       <c r="G67" t="n">
-        <v>7863.231488</v>
+        <v>7863.171221</v>
       </c>
       <c r="H67" t="n">
-        <v>10809.506437</v>
+        <v>10809.301765</v>
       </c>
       <c r="I67" t="n">
-        <v>14488.047988</v>
+        <v>14487.226659</v>
       </c>
       <c r="J67" t="n">
         <v>25621.731859</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>14839.284423</v>
+        <v>14839.272835</v>
       </c>
       <c r="F68" t="n">
-        <v>21839.079026</v>
+        <v>21839.016295</v>
       </c>
       <c r="G68" t="n">
-        <v>32656.198372</v>
+        <v>32655.904179</v>
       </c>
       <c r="H68" t="n">
-        <v>44597.170168</v>
+        <v>44596.105081</v>
       </c>
       <c r="I68" t="n">
-        <v>56971.075577</v>
+        <v>56967.061364</v>
       </c>
       <c r="J68" t="n">
         <v>96871.839286</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>9869.296408</v>
+        <v>9869.350275000001</v>
       </c>
       <c r="F69" t="n">
-        <v>13095.435798</v>
+        <v>13095.622043</v>
       </c>
       <c r="G69" t="n">
-        <v>16971.993538</v>
+        <v>16972.485251</v>
       </c>
       <c r="H69" t="n">
-        <v>20763.407587</v>
+        <v>20764.630821</v>
       </c>
       <c r="I69" t="n">
-        <v>25006.069932</v>
+        <v>25009.804941</v>
       </c>
       <c r="J69" t="n">
         <v>5480.862465</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>16491.015716</v>
+        <v>16491.095916</v>
       </c>
       <c r="F70" t="n">
-        <v>22498.186626</v>
+        <v>22498.47125</v>
       </c>
       <c r="G70" t="n">
-        <v>30123.26182</v>
+        <v>30124.034131</v>
       </c>
       <c r="H70" t="n">
-        <v>38002.026661</v>
+        <v>38003.996864</v>
       </c>
       <c r="I70" t="n">
-        <v>46977.16287</v>
+        <v>46983.302287</v>
       </c>
       <c r="J70" t="n">
         <v>16440.666712</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>37061.801681</v>
+        <v>37061.828903</v>
       </c>
       <c r="F71" t="n">
-        <v>55537.695292</v>
+        <v>55537.776695</v>
       </c>
       <c r="G71" t="n">
-        <v>74976.121665</v>
+        <v>74976.333528</v>
       </c>
       <c r="H71" t="n">
-        <v>92490.43535</v>
+        <v>92491.01749899999</v>
       </c>
       <c r="I71" t="n">
-        <v>110601.160555</v>
+        <v>110603.127651</v>
       </c>
       <c r="J71" t="n">
         <v>116604.898251</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21812.37916</v>
+        <v>21812.38202</v>
       </c>
       <c r="F72" t="n">
-        <v>27496.692988</v>
+        <v>27496.7148</v>
       </c>
       <c r="G72" t="n">
-        <v>34278.028742</v>
+        <v>34278.091675</v>
       </c>
       <c r="H72" t="n">
-        <v>40920.214627</v>
+        <v>40920.363525</v>
       </c>
       <c r="I72" t="n">
-        <v>48706.433612</v>
+        <v>48706.796997</v>
       </c>
       <c r="J72" t="n">
         <v>55925.983462</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>34452.714805</v>
+        <v>34452.61669</v>
       </c>
       <c r="F73" t="n">
-        <v>36046.52308</v>
+        <v>36046.349492</v>
       </c>
       <c r="G73" t="n">
-        <v>34111.658183</v>
+        <v>34111.512847</v>
       </c>
       <c r="H73" t="n">
-        <v>32639.448786</v>
+        <v>32639.413009</v>
       </c>
       <c r="I73" t="n">
-        <v>34150.631569</v>
+        <v>34150.82915</v>
       </c>
       <c r="J73" t="n">
         <v>36274.422293</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5927.950685</v>
+        <v>5927.985901</v>
       </c>
       <c r="F74" t="n">
-        <v>8964.858561999999</v>
+        <v>8964.995707</v>
       </c>
       <c r="G74" t="n">
-        <v>11997.34714</v>
+        <v>11997.719342</v>
       </c>
       <c r="H74" t="n">
-        <v>14456.412868</v>
+        <v>14457.32373</v>
       </c>
       <c r="I74" t="n">
-        <v>16877.422087</v>
+        <v>16880.11893</v>
       </c>
       <c r="J74" t="n">
         <v>2434.024589</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>29639.879462</v>
+        <v>29637.687857</v>
       </c>
       <c r="F75" t="n">
-        <v>37559.778582</v>
+        <v>37552.796649</v>
       </c>
       <c r="G75" t="n">
-        <v>45272.052194</v>
+        <v>45252.993096</v>
       </c>
       <c r="H75" t="n">
-        <v>52815.675386</v>
+        <v>52766.34969</v>
       </c>
       <c r="I75" t="n">
-        <v>59832.827086</v>
+        <v>59690.62234</v>
       </c>
       <c r="J75" t="n">
         <v>87141.970412</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>94102.323745</v>
+        <v>94051.580002</v>
       </c>
       <c r="F76" t="n">
-        <v>123269.055567</v>
+        <v>123116.223778</v>
       </c>
       <c r="G76" t="n">
-        <v>122030.287073</v>
+        <v>121715.067802</v>
       </c>
       <c r="H76" t="n">
-        <v>122497.324858</v>
+        <v>121846.736385</v>
       </c>
       <c r="I76" t="n">
-        <v>132710.621919</v>
+        <v>131051.952744</v>
       </c>
       <c r="J76" t="n">
         <v>389698.22081</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>41171.79222</v>
+        <v>41168.544856</v>
       </c>
       <c r="F77" t="n">
-        <v>59234.098566</v>
+        <v>59224.921792</v>
       </c>
       <c r="G77" t="n">
-        <v>74928.252185</v>
+        <v>74903.443699</v>
       </c>
       <c r="H77" t="n">
-        <v>84990.088076</v>
+        <v>84924.008993</v>
       </c>
       <c r="I77" t="n">
-        <v>89345.80818399999</v>
+        <v>89153.587071</v>
       </c>
       <c r="J77" t="n">
         <v>119172.671718</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>348935.357881</v>
+        <v>348950.8202</v>
       </c>
       <c r="F78" t="n">
-        <v>383849.692525</v>
+        <v>383862.753345</v>
       </c>
       <c r="G78" t="n">
-        <v>392249.134489</v>
+        <v>392203.317038</v>
       </c>
       <c r="H78" t="n">
-        <v>413596.393137</v>
+        <v>413391.857545</v>
       </c>
       <c r="I78" t="n">
-        <v>450387.693752</v>
+        <v>449693.164469</v>
       </c>
       <c r="J78" t="n">
         <v>610848.4507470001</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>49452.235584</v>
+        <v>49459.342049</v>
       </c>
       <c r="F79" t="n">
-        <v>81832.566842</v>
+        <v>81860.47498899999</v>
       </c>
       <c r="G79" t="n">
-        <v>128538.583239</v>
+        <v>128616.757694</v>
       </c>
       <c r="H79" t="n">
-        <v>183358.765876</v>
+        <v>183557.608599</v>
       </c>
       <c r="I79" t="n">
-        <v>235381.804575</v>
+        <v>235953.383575</v>
       </c>
       <c r="J79" t="n">
         <v>191485.154511</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>20935.02219</v>
+        <v>20936.165116</v>
       </c>
       <c r="F80" t="n">
-        <v>22606.010995</v>
+        <v>22607.127662</v>
       </c>
       <c r="G80" t="n">
-        <v>23559.492202</v>
+        <v>23557.497121</v>
       </c>
       <c r="H80" t="n">
-        <v>26024.906282</v>
+        <v>26014.513841</v>
       </c>
       <c r="I80" t="n">
-        <v>29849.034513</v>
+        <v>29812.496079</v>
       </c>
       <c r="J80" t="n">
         <v>40657.411358</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>65122.276497</v>
+        <v>65133.534906</v>
       </c>
       <c r="F81" t="n">
-        <v>111868.85151</v>
+        <v>111914.266302</v>
       </c>
       <c r="G81" t="n">
-        <v>179688.074642</v>
+        <v>179817.432678</v>
       </c>
       <c r="H81" t="n">
-        <v>262808.176217</v>
+        <v>263146.141005</v>
       </c>
       <c r="I81" t="n">
-        <v>347544.085929</v>
+        <v>348552.472539</v>
       </c>
       <c r="J81" t="n">
         <v>265178.211395</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>85547.97339100001</v>
+        <v>85556.205994</v>
       </c>
       <c r="F82" t="n">
-        <v>109047.800722</v>
+        <v>109068.097494</v>
       </c>
       <c r="G82" t="n">
-        <v>127761.854719</v>
+        <v>127790.891705</v>
       </c>
       <c r="H82" t="n">
-        <v>149636.293657</v>
+        <v>149673.61882</v>
       </c>
       <c r="I82" t="n">
-        <v>173167.28454</v>
+        <v>173223.537457</v>
       </c>
       <c r="J82" t="n">
         <v>191814.545809</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>218009.07403</v>
+        <v>218022.054021</v>
       </c>
       <c r="F83" t="n">
-        <v>369716.069694</v>
+        <v>369777.262992</v>
       </c>
       <c r="G83" t="n">
-        <v>573723.969266</v>
+        <v>573894.2991759999</v>
       </c>
       <c r="H83" t="n">
-        <v>803593.0837439999</v>
+        <v>803999.872354</v>
       </c>
       <c r="I83" t="n">
-        <v>1015576.786404</v>
+        <v>1016664.730628</v>
       </c>
       <c r="J83" t="n">
         <v>1031648.599035</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>165942.694011</v>
+        <v>165957.840802</v>
       </c>
       <c r="F86" t="n">
-        <v>183932.226285</v>
+        <v>183973.291452</v>
       </c>
       <c r="G86" t="n">
-        <v>207709.94894</v>
+        <v>207800.63068</v>
       </c>
       <c r="H86" t="n">
-        <v>232616.317253</v>
+        <v>232813.814802</v>
       </c>
       <c r="I86" t="n">
-        <v>253167.446835</v>
+        <v>253677.564858</v>
       </c>
       <c r="J86" t="n">
         <v>145047.322895</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15463.162764</v>
+        <v>15462.226329</v>
       </c>
       <c r="F87" t="n">
-        <v>19318.96632</v>
+        <v>19316.336741</v>
       </c>
       <c r="G87" t="n">
-        <v>25154.415584</v>
+        <v>25148.321856</v>
       </c>
       <c r="H87" t="n">
-        <v>31866.143005</v>
+        <v>31852.010409</v>
       </c>
       <c r="I87" t="n">
-        <v>38775.563795</v>
+        <v>38736.35726</v>
       </c>
       <c r="J87" t="n">
         <v>55458.166172</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>281408.508218</v>
+        <v>281423.944333</v>
       </c>
       <c r="F88" t="n">
-        <v>284390.854997</v>
+        <v>284426.275718</v>
       </c>
       <c r="G88" t="n">
-        <v>303161.791148</v>
+        <v>303231.217056</v>
       </c>
       <c r="H88" t="n">
-        <v>337498.700965</v>
+        <v>337644.021555</v>
       </c>
       <c r="I88" t="n">
-        <v>378513.330981</v>
+        <v>378894.07563</v>
       </c>
       <c r="J88" t="n">
         <v>325146.272638</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>34561.055697</v>
+        <v>34563.775391</v>
       </c>
       <c r="F89" t="n">
-        <v>37067.208377</v>
+        <v>37074.23444</v>
       </c>
       <c r="G89" t="n">
-        <v>42511.790848</v>
+        <v>42527.570032</v>
       </c>
       <c r="H89" t="n">
-        <v>48647.800103</v>
+        <v>48683.014559</v>
       </c>
       <c r="I89" t="n">
-        <v>54235.841905</v>
+        <v>54329.171114</v>
       </c>
       <c r="J89" t="n">
         <v>35782.328875</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103552.891677</v>
+        <v>103544.167643</v>
       </c>
       <c r="F90" t="n">
-        <v>112646.092298</v>
+        <v>112623.190053</v>
       </c>
       <c r="G90" t="n">
-        <v>132318.592537</v>
+        <v>132268.005939</v>
       </c>
       <c r="H90" t="n">
-        <v>156820.919889</v>
+        <v>156708.547461</v>
       </c>
       <c r="I90" t="n">
-        <v>182603.762936</v>
+        <v>182305.615697</v>
       </c>
       <c r="J90" t="n">
         <v>280020.824092</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>14573.23839</v>
+        <v>14566.982554</v>
       </c>
       <c r="F91" t="n">
-        <v>16284.529396</v>
+        <v>16267.913908</v>
       </c>
       <c r="G91" t="n">
-        <v>18827.646601</v>
+        <v>18791.003412</v>
       </c>
       <c r="H91" t="n">
-        <v>21470.800336</v>
+        <v>21391.180075</v>
       </c>
       <c r="I91" t="n">
-        <v>24435.83928</v>
+        <v>24231.716669</v>
       </c>
       <c r="J91" t="n">
         <v>75803.624698</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>18878.358681</v>
+        <v>18876.425884</v>
       </c>
       <c r="F92" t="n">
-        <v>21179.962799</v>
+        <v>21174.897339</v>
       </c>
       <c r="G92" t="n">
-        <v>25096.862945</v>
+        <v>25085.724998</v>
       </c>
       <c r="H92" t="n">
-        <v>29006.841257</v>
+        <v>28982.430589</v>
       </c>
       <c r="I92" t="n">
-        <v>32490.106048</v>
+        <v>32426.406702</v>
       </c>
       <c r="J92" t="n">
         <v>50768.11099</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4454.049199</v>
+        <v>4453.384248</v>
       </c>
       <c r="F93" t="n">
-        <v>5255.407673</v>
+        <v>5253.566774</v>
       </c>
       <c r="G93" t="n">
-        <v>6637.116345</v>
+        <v>6632.821647</v>
       </c>
       <c r="H93" t="n">
-        <v>8406.485357</v>
+        <v>8396.475795</v>
       </c>
       <c r="I93" t="n">
-        <v>10380.065591</v>
+        <v>10352.476403</v>
       </c>
       <c r="J93" t="n">
         <v>19276.338623</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>560208.706204</v>
+        <v>560196.151806</v>
       </c>
       <c r="F94" t="n">
-        <v>668307.688469</v>
+        <v>668278.204394</v>
       </c>
       <c r="G94" t="n">
-        <v>801214.020852</v>
+        <v>801155.26956</v>
       </c>
       <c r="H94" t="n">
-        <v>938813.83423</v>
+        <v>938690.743154</v>
       </c>
       <c r="I94" t="n">
-        <v>1062712.709529</v>
+        <v>1062392.748974</v>
       </c>
       <c r="J94" t="n">
         <v>1243960.833478</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>224692.889399</v>
+        <v>224690.212994</v>
       </c>
       <c r="F95" t="n">
-        <v>268499.976694</v>
+        <v>268495.412775</v>
       </c>
       <c r="G95" t="n">
-        <v>326957.604658</v>
+        <v>326952.943676</v>
       </c>
       <c r="H95" t="n">
-        <v>386896.153109</v>
+        <v>386893.295175</v>
       </c>
       <c r="I95" t="n">
-        <v>440345.197994</v>
+        <v>440347.839179</v>
       </c>
       <c r="J95" t="n">
         <v>478956.447144</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>90778.978791</v>
+        <v>90777.41946799999</v>
       </c>
       <c r="F96" t="n">
-        <v>95990.452987</v>
+        <v>95985.87800300001</v>
       </c>
       <c r="G96" t="n">
-        <v>103202.473955</v>
+        <v>103191.22626</v>
       </c>
       <c r="H96" t="n">
-        <v>114317.263216</v>
+        <v>114290.743477</v>
       </c>
       <c r="I96" t="n">
-        <v>127515.011731</v>
+        <v>127442.524617</v>
       </c>
       <c r="J96" t="n">
         <v>159329.283699</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>50477.566969</v>
+        <v>50479.568547</v>
       </c>
       <c r="F97" t="n">
-        <v>49371.096405</v>
+        <v>49375.261103</v>
       </c>
       <c r="G97" t="n">
-        <v>51507.685787</v>
+        <v>51515.215084</v>
       </c>
       <c r="H97" t="n">
-        <v>56658.514378</v>
+        <v>56673.496049</v>
       </c>
       <c r="I97" t="n">
-        <v>63361.951475</v>
+        <v>63400.330997</v>
       </c>
       <c r="J97" t="n">
         <v>60890.686797</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>208552.156727</v>
+        <v>208550.495816</v>
       </c>
       <c r="F98" t="n">
-        <v>207967.847193</v>
+        <v>207961.392451</v>
       </c>
       <c r="G98" t="n">
-        <v>212154.352085</v>
+        <v>212135.037676</v>
       </c>
       <c r="H98" t="n">
-        <v>218393.077521</v>
+        <v>218343.561029</v>
       </c>
       <c r="I98" t="n">
-        <v>227161.266518</v>
+        <v>227020.670896</v>
       </c>
       <c r="J98" t="n">
         <v>269461.637472</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>231353.763718</v>
+        <v>231342.970849</v>
       </c>
       <c r="F99" t="n">
-        <v>267070.753359</v>
+        <v>267044.495695</v>
       </c>
       <c r="G99" t="n">
-        <v>319069.587587</v>
+        <v>319016.702017</v>
       </c>
       <c r="H99" t="n">
-        <v>370396.555702</v>
+        <v>370288.706819</v>
       </c>
       <c r="I99" t="n">
-        <v>418368.582707</v>
+        <v>418097.75442</v>
       </c>
       <c r="J99" t="n">
         <v>518445.488362</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>97620.823699</v>
+        <v>97613.133468</v>
       </c>
       <c r="F100" t="n">
-        <v>96726.76602900001</v>
+        <v>96706.632364</v>
       </c>
       <c r="G100" t="n">
-        <v>100073.101642</v>
+        <v>100029.526886</v>
       </c>
       <c r="H100" t="n">
-        <v>104699.245475</v>
+        <v>104606.297155</v>
       </c>
       <c r="I100" t="n">
-        <v>110981.589422</v>
+        <v>110743.528048</v>
       </c>
       <c r="J100" t="n">
         <v>169315.237585</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>231034.909809</v>
+        <v>231058.689338</v>
       </c>
       <c r="F101" t="n">
-        <v>244780.782407</v>
+        <v>244841.516736</v>
       </c>
       <c r="G101" t="n">
-        <v>268226.517783</v>
+        <v>268353.061079</v>
       </c>
       <c r="H101" t="n">
-        <v>290503.010082</v>
+        <v>290762.001062</v>
       </c>
       <c r="I101" t="n">
-        <v>308656.479295</v>
+        <v>309293.852442</v>
       </c>
       <c r="J101" t="n">
         <v>190137.939859</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1937164.922999</v>
+        <v>1937270.562285</v>
       </c>
       <c r="F102" t="n">
-        <v>2171738.10975</v>
+        <v>2172035.024991</v>
       </c>
       <c r="G102" t="n">
-        <v>2545549.881653</v>
+        <v>2546238.651326</v>
       </c>
       <c r="H102" t="n">
-        <v>2935177.742984</v>
+        <v>2936724.186398</v>
       </c>
       <c r="I102" t="n">
-        <v>3302274.448999</v>
+        <v>3306381.09571</v>
       </c>
       <c r="J102" t="n">
         <v>2716366.659862</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2164781.251411</v>
+        <v>2164854.278488</v>
       </c>
       <c r="F103" t="n">
-        <v>2079381.024092</v>
+        <v>2079524.750412</v>
       </c>
       <c r="G103" t="n">
-        <v>2061090.35811</v>
+        <v>2061302.837792</v>
       </c>
       <c r="H103" t="n">
-        <v>2074110.780555</v>
+        <v>2074419.877601</v>
       </c>
       <c r="I103" t="n">
-        <v>2115378.831125</v>
+        <v>2115941.867988</v>
       </c>
       <c r="J103" t="n">
         <v>2078792.941128</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>174821.90096</v>
+        <v>174805.907959</v>
       </c>
       <c r="F104" t="n">
-        <v>188699.240957</v>
+        <v>188658.784597</v>
       </c>
       <c r="G104" t="n">
-        <v>211547.221218</v>
+        <v>211462.190799</v>
       </c>
       <c r="H104" t="n">
-        <v>237959.419189</v>
+        <v>237782.056162</v>
       </c>
       <c r="I104" t="n">
-        <v>266641.108207</v>
+        <v>266194.529349</v>
       </c>
       <c r="J104" t="n">
         <v>388967.985224</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>95128.013591</v>
+        <v>95123.695253</v>
       </c>
       <c r="F105" t="n">
-        <v>104298.647693</v>
+        <v>104287.006102</v>
       </c>
       <c r="G105" t="n">
-        <v>120142.977639</v>
+        <v>120117.24288</v>
       </c>
       <c r="H105" t="n">
-        <v>136359.889808</v>
+        <v>136303.351458</v>
       </c>
       <c r="I105" t="n">
-        <v>152451.517506</v>
+        <v>152301.450177</v>
       </c>
       <c r="J105" t="n">
         <v>200825.201253</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>949797.4830529999</v>
+        <v>949715.9791089999</v>
       </c>
       <c r="F106" t="n">
-        <v>1074994.018737</v>
+        <v>1074788.278886</v>
       </c>
       <c r="G106" t="n">
-        <v>1284067.881931</v>
+        <v>1283639.681277</v>
       </c>
       <c r="H106" t="n">
-        <v>1498528.552742</v>
+        <v>1497643.998347</v>
       </c>
       <c r="I106" t="n">
-        <v>1706800.908829</v>
+        <v>1704590.570527</v>
       </c>
       <c r="J106" t="n">
         <v>2357774.357332</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4543.594558</v>
+        <v>4538.394302</v>
       </c>
       <c r="F107" t="n">
-        <v>5484.821553</v>
+        <v>5470.153903</v>
       </c>
       <c r="G107" t="n">
-        <v>6542.905938</v>
+        <v>6510.023124</v>
       </c>
       <c r="H107" t="n">
-        <v>7772.191601</v>
+        <v>7700.123952</v>
       </c>
       <c r="I107" t="n">
-        <v>9748.057409999999</v>
+        <v>9558.123621999999</v>
       </c>
       <c r="J107" t="n">
         <v>54501.584848</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>371715.640001</v>
+        <v>371692.793208</v>
       </c>
       <c r="F108" t="n">
-        <v>400068.062201</v>
+        <v>400009.168142</v>
       </c>
       <c r="G108" t="n">
-        <v>439324.466386</v>
+        <v>439196.938492</v>
       </c>
       <c r="H108" t="n">
-        <v>478035.747834</v>
+        <v>477761.903619</v>
       </c>
       <c r="I108" t="n">
-        <v>517095.222468</v>
+        <v>516389.340857</v>
       </c>
       <c r="J108" t="n">
         <v>706656.592985</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>172874.696103</v>
+        <v>172872.972549</v>
       </c>
       <c r="F109" t="n">
-        <v>186498.848497</v>
+        <v>186494.907454</v>
       </c>
       <c r="G109" t="n">
-        <v>218536.951744</v>
+        <v>218531.895388</v>
       </c>
       <c r="H109" t="n">
-        <v>259862.59524</v>
+        <v>259862.225478</v>
       </c>
       <c r="I109" t="n">
-        <v>307018.806963</v>
+        <v>307049.017473</v>
       </c>
       <c r="J109" t="n">
         <v>339663.935163</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>545443.747223</v>
+        <v>545512.335002</v>
       </c>
       <c r="F110" t="n">
-        <v>623986.083811</v>
+        <v>624178.299622</v>
       </c>
       <c r="G110" t="n">
-        <v>743639.535577</v>
+        <v>744083.618733</v>
       </c>
       <c r="H110" t="n">
-        <v>859629.502382</v>
+        <v>860615.805278</v>
       </c>
       <c r="I110" t="n">
-        <v>954823.569405</v>
+        <v>957398.2111</v>
       </c>
       <c r="J110" t="n">
         <v>470569.005394</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>936212.939757</v>
+        <v>936192.067054</v>
       </c>
       <c r="F111" t="n">
-        <v>1039223.366818</v>
+        <v>1039174.009772</v>
       </c>
       <c r="G111" t="n">
-        <v>1186372.104911</v>
+        <v>1186271.709612</v>
       </c>
       <c r="H111" t="n">
-        <v>1333080.612059</v>
+        <v>1332870.305782</v>
       </c>
       <c r="I111" t="n">
-        <v>1481413.254949</v>
+        <v>1480875.327048</v>
       </c>
       <c r="J111" t="n">
         <v>1737439.270447</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1131081.856393</v>
+        <v>1130983.425319</v>
       </c>
       <c r="F112" t="n">
-        <v>1275097.515904</v>
+        <v>1274841.467873</v>
       </c>
       <c r="G112" t="n">
-        <v>1507550.482794</v>
+        <v>1506999.209918</v>
       </c>
       <c r="H112" t="n">
-        <v>1750654.322824</v>
+        <v>1749478.84586</v>
       </c>
       <c r="I112" t="n">
-        <v>1996217.622196</v>
+        <v>1993195.926343</v>
       </c>
       <c r="J112" t="n">
         <v>2880885.479087</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>119893.183652</v>
+        <v>119845.353554</v>
       </c>
       <c r="F113" t="n">
-        <v>127670.074858</v>
+        <v>127539.950786</v>
       </c>
       <c r="G113" t="n">
-        <v>117832.715668</v>
+        <v>117572.233046</v>
       </c>
       <c r="H113" t="n">
-        <v>120664.464872</v>
+        <v>120120.405064</v>
       </c>
       <c r="I113" t="n">
-        <v>131904.731493</v>
+        <v>130583.55333</v>
       </c>
       <c r="J113" t="n">
         <v>241741.449876</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21244.908668</v>
+        <v>21242.809961</v>
       </c>
       <c r="F114" t="n">
-        <v>31810.824223</v>
+        <v>31809.066336</v>
       </c>
       <c r="G114" t="n">
-        <v>43372.037133</v>
+        <v>43377.654781</v>
       </c>
       <c r="H114" t="n">
-        <v>56947.557414</v>
+        <v>56974.653557</v>
       </c>
       <c r="I114" t="n">
-        <v>67732.62137399999</v>
+        <v>67820.953549</v>
       </c>
       <c r="J114" t="n">
         <v>68029.777988</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>568320.54168</v>
+        <v>568370.4704850001</v>
       </c>
       <c r="F115" t="n">
-        <v>692158.072299</v>
+        <v>692289.954258</v>
       </c>
       <c r="G115" t="n">
-        <v>791796.91967</v>
+        <v>792051.784643</v>
       </c>
       <c r="H115" t="n">
-        <v>941101.503084</v>
+        <v>941618.466749</v>
       </c>
       <c r="I115" t="n">
-        <v>1083187.725902</v>
+        <v>1084420.571891</v>
       </c>
       <c r="J115" t="n">
         <v>1127757.040906</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>21237.809334</v>
+        <v>21237.998755</v>
       </c>
       <c r="F116" t="n">
-        <v>23197.121679</v>
+        <v>23197.57985</v>
       </c>
       <c r="G116" t="n">
-        <v>25877.329428</v>
+        <v>25878.238327</v>
       </c>
       <c r="H116" t="n">
-        <v>29670.070239</v>
+        <v>29671.956404</v>
       </c>
       <c r="I116" t="n">
-        <v>32684.578539</v>
+        <v>32689.258337</v>
       </c>
       <c r="J116" t="n">
         <v>32958.391531</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>56288.27969</v>
+        <v>56289.809538</v>
       </c>
       <c r="F117" t="n">
-        <v>75877.935912</v>
+        <v>75883.912568</v>
       </c>
       <c r="G117" t="n">
-        <v>93224.305257</v>
+        <v>93239.471641</v>
       </c>
       <c r="H117" t="n">
-        <v>112087.839555</v>
+        <v>112124.176185</v>
       </c>
       <c r="I117" t="n">
-        <v>125406.821276</v>
+        <v>125504.127224</v>
       </c>
       <c r="J117" t="n">
         <v>93649.793454</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>40567.997889</v>
+        <v>40563.74003</v>
       </c>
       <c r="F118" t="n">
-        <v>43406.498143</v>
+        <v>43395.441018</v>
       </c>
       <c r="G118" t="n">
-        <v>47228.082056</v>
+        <v>47204.650071</v>
       </c>
       <c r="H118" t="n">
-        <v>53318.136105</v>
+        <v>53267.068731</v>
       </c>
       <c r="I118" t="n">
-        <v>59174.622031</v>
+        <v>59044.515684</v>
       </c>
       <c r="J118" t="n">
         <v>115578.057118</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>20350.628484</v>
+        <v>20350.246524</v>
       </c>
       <c r="F119" t="n">
-        <v>26222.821881</v>
+        <v>26222.005254</v>
       </c>
       <c r="G119" t="n">
-        <v>33781.721417</v>
+        <v>33780.421569</v>
       </c>
       <c r="H119" t="n">
-        <v>43247.198641</v>
+        <v>43245.23131</v>
       </c>
       <c r="I119" t="n">
-        <v>51587.379354</v>
+        <v>51584.051788</v>
       </c>
       <c r="J119" t="n">
         <v>58994.695456</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>10814.412755</v>
+        <v>10814.762294</v>
       </c>
       <c r="F120" t="n">
-        <v>11883.280957</v>
+        <v>11884.185658</v>
       </c>
       <c r="G120" t="n">
-        <v>13360.058156</v>
+        <v>13361.980204</v>
       </c>
       <c r="H120" t="n">
-        <v>15461.059017</v>
+        <v>15465.282566</v>
       </c>
       <c r="I120" t="n">
-        <v>17164.168398</v>
+        <v>17175.080124</v>
       </c>
       <c r="J120" t="n">
         <v>14020.185911</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>135427.063122</v>
+        <v>135429.16939</v>
       </c>
       <c r="F121" t="n">
-        <v>171901.203211</v>
+        <v>171909.461092</v>
       </c>
       <c r="G121" t="n">
-        <v>217555.106871</v>
+        <v>217578.633365</v>
       </c>
       <c r="H121" t="n">
-        <v>270793.18236</v>
+        <v>270854.388051</v>
       </c>
       <c r="I121" t="n">
-        <v>311060.513909</v>
+        <v>311231.791073</v>
       </c>
       <c r="J121" t="n">
         <v>265948.82725</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>943260.319726</v>
+        <v>943260.7844689999</v>
       </c>
       <c r="F122" t="n">
-        <v>1041194.271256</v>
+        <v>1041190.5476</v>
       </c>
       <c r="G122" t="n">
-        <v>1179909.502165</v>
+        <v>1179892.710173</v>
       </c>
       <c r="H122" t="n">
-        <v>1383935.369232</v>
+        <v>1383884.751903</v>
       </c>
       <c r="I122" t="n">
-        <v>1571651.401244</v>
+        <v>1571500.66052</v>
       </c>
       <c r="J122" t="n">
         <v>1795509.55703</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>65347.153691</v>
+        <v>65414.73513</v>
       </c>
       <c r="F123" t="n">
-        <v>72207.429473</v>
+        <v>72378.30179699999</v>
       </c>
       <c r="G123" t="n">
-        <v>81649.797947</v>
+        <v>81999.404344</v>
       </c>
       <c r="H123" t="n">
-        <v>90356.715039</v>
+        <v>91046.535919</v>
       </c>
       <c r="I123" t="n">
-        <v>94092.054609</v>
+        <v>95568.766367</v>
       </c>
       <c r="J123" t="n">
         <v>35786.676137</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>500626.666841</v>
+        <v>500880.567657</v>
       </c>
       <c r="F124" t="n">
-        <v>558321.568539</v>
+        <v>558965.339564</v>
       </c>
       <c r="G124" t="n">
-        <v>629645.134709</v>
+        <v>630937.77938</v>
       </c>
       <c r="H124" t="n">
-        <v>703055.397536</v>
+        <v>705567.535658</v>
       </c>
       <c r="I124" t="n">
-        <v>757234.440484</v>
+        <v>762507.798912</v>
       </c>
       <c r="J124" t="n">
         <v>587155.169768</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>234245.023468</v>
+        <v>233923.541212</v>
       </c>
       <c r="F125" t="n">
-        <v>247089.633458</v>
+        <v>246274.990109</v>
       </c>
       <c r="G125" t="n">
-        <v>263898.525884</v>
+        <v>262256.274816</v>
       </c>
       <c r="H125" t="n">
-        <v>293224.714435</v>
+        <v>290022.755434</v>
       </c>
       <c r="I125" t="n">
-        <v>349889.989277</v>
+        <v>343139.919092</v>
       </c>
       <c r="J125" t="n">
         <v>675653.694566</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>449013.792225</v>
+        <v>449015.443643</v>
       </c>
       <c r="F130" t="n">
-        <v>517943.006122</v>
+        <v>517947.249656</v>
       </c>
       <c r="G130" t="n">
-        <v>665556.006891</v>
+        <v>665565.1888520001</v>
       </c>
       <c r="H130" t="n">
-        <v>860602.310074</v>
+        <v>860621.984672</v>
       </c>
       <c r="I130" t="n">
-        <v>1085159.645183</v>
+        <v>1085212.083717</v>
       </c>
       <c r="J130" t="n">
         <v>1476631.417722</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100354.494611</v>
+        <v>100353.94487</v>
       </c>
       <c r="F131" t="n">
-        <v>131204.707535</v>
+        <v>131202.78083</v>
       </c>
       <c r="G131" t="n">
-        <v>173357.206515</v>
+        <v>173351.726466</v>
       </c>
       <c r="H131" t="n">
-        <v>224190.218679</v>
+        <v>224175.239554</v>
       </c>
       <c r="I131" t="n">
-        <v>279854.177195</v>
+        <v>279806.472922</v>
       </c>
       <c r="J131" t="n">
         <v>161921.916471</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>989175.470299</v>
+        <v>989178.5280779999</v>
       </c>
       <c r="F132" t="n">
-        <v>1048219.583383</v>
+        <v>1048226.677305</v>
       </c>
       <c r="G132" t="n">
-        <v>1206033.830583</v>
+        <v>1206047.444472</v>
       </c>
       <c r="H132" t="n">
-        <v>1393804.725956</v>
+        <v>1393830.736751</v>
       </c>
       <c r="I132" t="n">
-        <v>1592740.29506</v>
+        <v>1592803.500477</v>
       </c>
       <c r="J132" t="n">
         <v>1969446.479548</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>242323.40777</v>
+        <v>242324.362126</v>
       </c>
       <c r="F133" t="n">
-        <v>365900.862574</v>
+        <v>365903.751179</v>
       </c>
       <c r="G133" t="n">
-        <v>585238.1436449999</v>
+        <v>585245.090663</v>
       </c>
       <c r="H133" t="n">
-        <v>864571.3206719999</v>
+        <v>864586.754354</v>
       </c>
       <c r="I133" t="n">
-        <v>1172207.764162</v>
+        <v>1172249.241725</v>
       </c>
       <c r="J133" t="n">
         <v>1608698.54749</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>226364.905887</v>
+        <v>226365.228562</v>
       </c>
       <c r="F134" t="n">
-        <v>226905.988368</v>
+        <v>226906.666058</v>
       </c>
       <c r="G134" t="n">
-        <v>258286.964118</v>
+        <v>258288.042551</v>
       </c>
       <c r="H134" t="n">
-        <v>305927.826331</v>
+        <v>305929.3245</v>
       </c>
       <c r="I134" t="n">
-        <v>364760.834456</v>
+        <v>364763.137671</v>
       </c>
       <c r="J134" t="n">
         <v>430613.199716</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>66985.667032</v>
+        <v>66985.550707</v>
       </c>
       <c r="F135" t="n">
-        <v>91106.27344600001</v>
+        <v>91105.76242499999</v>
       </c>
       <c r="G135" t="n">
-        <v>135582.909967</v>
+        <v>135580.991676</v>
       </c>
       <c r="H135" t="n">
-        <v>192599.035859</v>
+        <v>192592.697589</v>
       </c>
       <c r="I135" t="n">
-        <v>257801.115225</v>
+        <v>257778.363227</v>
       </c>
       <c r="J135" t="n">
         <v>236896.151141</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>240611.660451</v>
+        <v>240610.720342</v>
       </c>
       <c r="F136" t="n">
-        <v>241397.673916</v>
+        <v>241395.17542</v>
       </c>
       <c r="G136" t="n">
-        <v>255891.256885</v>
+        <v>255885.57725</v>
       </c>
       <c r="H136" t="n">
-        <v>273509.442625</v>
+        <v>273496.677687</v>
       </c>
       <c r="I136" t="n">
-        <v>298067.995604</v>
+        <v>298032.7463</v>
       </c>
       <c r="J136" t="n">
         <v>217404.632647</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>65723.655006</v>
+        <v>65723.928207</v>
       </c>
       <c r="F137" t="n">
-        <v>72259.348361</v>
+        <v>72260.013553</v>
       </c>
       <c r="G137" t="n">
-        <v>82993.77488500001</v>
+        <v>82995.109658</v>
       </c>
       <c r="H137" t="n">
-        <v>95339.410468</v>
+        <v>95342.095887</v>
       </c>
       <c r="I137" t="n">
-        <v>109857.026101</v>
+        <v>109863.869706</v>
       </c>
       <c r="J137" t="n">
         <v>145987.441253</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>115439.806757</v>
+        <v>115439.419972</v>
       </c>
       <c r="F138" t="n">
-        <v>123306.985669</v>
+        <v>123305.855146</v>
       </c>
       <c r="G138" t="n">
-        <v>142610.458547</v>
+        <v>142607.562577</v>
       </c>
       <c r="H138" t="n">
-        <v>163369.806468</v>
+        <v>163362.666182</v>
       </c>
       <c r="I138" t="n">
-        <v>182321.527452</v>
+        <v>182301.106851</v>
       </c>
       <c r="J138" t="n">
         <v>131044.171504</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>146179.409733</v>
+        <v>146178.058693</v>
       </c>
       <c r="F139" t="n">
-        <v>164939.661859</v>
+        <v>164935.727619</v>
       </c>
       <c r="G139" t="n">
-        <v>209012.406149</v>
+        <v>209002.001699</v>
       </c>
       <c r="H139" t="n">
-        <v>267550.334545</v>
+        <v>267522.798288</v>
       </c>
       <c r="I139" t="n">
-        <v>332611.444345</v>
+        <v>332525.024543</v>
       </c>
       <c r="J139" t="n">
         <v>84964.689226</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1269425.750075</v>
+        <v>1269420.414734</v>
       </c>
       <c r="F140" t="n">
-        <v>1307286.011991</v>
+        <v>1307271.465965</v>
       </c>
       <c r="G140" t="n">
-        <v>1536358.963942</v>
+        <v>1536321.923899</v>
       </c>
       <c r="H140" t="n">
-        <v>1896271.365005</v>
+        <v>1896173.700383</v>
       </c>
       <c r="I140" t="n">
-        <v>2373486.134487</v>
+        <v>2373171.436182</v>
       </c>
       <c r="J140" t="n">
         <v>1747905.359241</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>70090.37887099999</v>
+        <v>70091.315995</v>
       </c>
       <c r="F141" t="n">
-        <v>81292.02694700001</v>
+        <v>81294.62861299999</v>
       </c>
       <c r="G141" t="n">
-        <v>105145.564326</v>
+        <v>105151.955762</v>
       </c>
       <c r="H141" t="n">
-        <v>136451.297998</v>
+        <v>136467.053715</v>
       </c>
       <c r="I141" t="n">
-        <v>173703.59723</v>
+        <v>173750.804221</v>
       </c>
       <c r="J141" t="n">
         <v>378438.96265</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>20382.218283</v>
+        <v>20383.70107</v>
       </c>
       <c r="F142" t="n">
-        <v>37504.192829</v>
+        <v>37510.569233</v>
       </c>
       <c r="G142" t="n">
-        <v>78776.796947</v>
+        <v>78801.66787600001</v>
       </c>
       <c r="H142" t="n">
-        <v>144695.50132</v>
+        <v>144780.866439</v>
       </c>
       <c r="I142" t="n">
-        <v>233571.9555</v>
+        <v>233885.724459</v>
       </c>
       <c r="J142" t="n">
         <v>1569643.565391</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4255.563318</v>
+        <v>4255.541343</v>
       </c>
       <c r="F146" t="n">
-        <v>4084.736808</v>
+        <v>4084.688241</v>
       </c>
       <c r="G146" t="n">
-        <v>4399.731139</v>
+        <v>4399.636272</v>
       </c>
       <c r="H146" t="n">
-        <v>4996.640514</v>
+        <v>4996.43414</v>
       </c>
       <c r="I146" t="n">
-        <v>6051.007146</v>
+        <v>6050.377138</v>
       </c>
       <c r="J146" t="n">
         <v>8075.418204</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>8331.275637000001</v>
+        <v>8331.177265</v>
       </c>
       <c r="F147" t="n">
-        <v>9252.047707</v>
+        <v>9251.770753999999</v>
       </c>
       <c r="G147" t="n">
-        <v>11256.016338</v>
+        <v>11255.342533</v>
       </c>
       <c r="H147" t="n">
-        <v>13518.913027</v>
+        <v>13517.301864</v>
       </c>
       <c r="I147" t="n">
-        <v>16583.566072</v>
+        <v>16578.659127</v>
       </c>
       <c r="J147" t="n">
         <v>25587.49003</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>468684.994845</v>
+        <v>468685.115192</v>
       </c>
       <c r="F148" t="n">
-        <v>537701.069634</v>
+        <v>537701.395155</v>
       </c>
       <c r="G148" t="n">
-        <v>695036.753483</v>
+        <v>695037.522155</v>
       </c>
       <c r="H148" t="n">
-        <v>879207.595809</v>
+        <v>879209.413346</v>
       </c>
       <c r="I148" t="n">
-        <v>1109778.987843</v>
+        <v>1109784.524795</v>
       </c>
       <c r="J148" t="n">
         <v>1334530.900035</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>31442.733186</v>
+        <v>31441.81328</v>
       </c>
       <c r="F149" t="n">
-        <v>37042.323768</v>
+        <v>37039.666473</v>
       </c>
       <c r="G149" t="n">
-        <v>49084.848336</v>
+        <v>49077.737192</v>
       </c>
       <c r="H149" t="n">
-        <v>63414.347447</v>
+        <v>63395.56472</v>
       </c>
       <c r="I149" t="n">
-        <v>80456.027821</v>
+        <v>80395.57709999999</v>
       </c>
       <c r="J149" t="n">
         <v>163674.115026</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>262318.110771</v>
+        <v>262318.710056</v>
       </c>
       <c r="F150" t="n">
-        <v>304989.614916</v>
+        <v>304991.765615</v>
       </c>
       <c r="G150" t="n">
-        <v>395023.531471</v>
+        <v>395028.440188</v>
       </c>
       <c r="H150" t="n">
-        <v>479820.627363</v>
+        <v>479828.259429</v>
       </c>
       <c r="I150" t="n">
-        <v>562869.012818</v>
+        <v>562875.7676660001</v>
       </c>
       <c r="J150" t="n">
         <v>654810.0545570001</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>90279.569334</v>
+        <v>90278.100454</v>
       </c>
       <c r="F151" t="n">
-        <v>109236.952447</v>
+        <v>109232.692076</v>
       </c>
       <c r="G151" t="n">
-        <v>147514.230726</v>
+        <v>147502.587686</v>
       </c>
       <c r="H151" t="n">
-        <v>186390.217977</v>
+        <v>186359.47497</v>
       </c>
       <c r="I151" t="n">
-        <v>223068.538195</v>
+        <v>222972.169522</v>
       </c>
       <c r="J151" t="n">
         <v>353710.878595</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>167457.611894</v>
+        <v>167450.786482</v>
       </c>
       <c r="F152" t="n">
-        <v>212373.36611</v>
+        <v>212352.306737</v>
       </c>
       <c r="G152" t="n">
-        <v>281797.50077</v>
+        <v>281741.617735</v>
       </c>
       <c r="H152" t="n">
-        <v>341180.208237</v>
+        <v>341043.013882</v>
       </c>
       <c r="I152" t="n">
-        <v>390447.092163</v>
+        <v>390051.486876</v>
       </c>
       <c r="J152" t="n">
         <v>801647.716757</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>193821.342923</v>
+        <v>193829.986142</v>
       </c>
       <c r="F153" t="n">
-        <v>229491.649119</v>
+        <v>229517.448311</v>
       </c>
       <c r="G153" t="n">
-        <v>313496.564355</v>
+        <v>313566.302316</v>
       </c>
       <c r="H153" t="n">
-        <v>414236.67065</v>
+        <v>414416.571498</v>
       </c>
       <c r="I153" t="n">
-        <v>525684.0311359999</v>
+        <v>526234.978597</v>
       </c>
       <c r="J153" t="n">
         <v>108199.361628</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>47755.891891</v>
+        <v>47755.863585</v>
       </c>
       <c r="F154" t="n">
-        <v>59513.02804</v>
+        <v>59513.055189</v>
       </c>
       <c r="G154" t="n">
-        <v>78943.394222</v>
+        <v>78943.38476299999</v>
       </c>
       <c r="H154" t="n">
-        <v>95779.66340600001</v>
+        <v>95778.85058</v>
       </c>
       <c r="I154" t="n">
-        <v>108772.493947</v>
+        <v>108767.216319</v>
       </c>
       <c r="J154" t="n">
         <v>126638.626517</v>
@@ -12154,58 +12154,58 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>64675.742009</v>
+        <v>64675.750804</v>
       </c>
       <c r="F155" t="n">
-        <v>104428.801289</v>
+        <v>104428.831228</v>
       </c>
       <c r="G155" t="n">
-        <v>163121.45525</v>
+        <v>163121.52832</v>
       </c>
       <c r="H155" t="n">
-        <v>239216.904167</v>
+        <v>239217.054286</v>
       </c>
       <c r="I155" t="n">
-        <v>319460.365038</v>
+        <v>319460.630758</v>
       </c>
       <c r="J155" t="n">
-        <v>413301.941979</v>
+        <v>413302.383136</v>
       </c>
       <c r="K155" t="n">
-        <v>518166.485166</v>
+        <v>518167.180334</v>
       </c>
       <c r="L155" t="n">
-        <v>630171.7209430001</v>
+        <v>630172.767313</v>
       </c>
       <c r="M155" t="n">
-        <v>753980.554423</v>
+        <v>753982.088486</v>
       </c>
       <c r="N155" t="n">
-        <v>886844.450352</v>
+        <v>886846.647495</v>
       </c>
       <c r="O155" t="n">
-        <v>1017538.995137</v>
+        <v>1017542.054523</v>
       </c>
       <c r="P155" t="n">
-        <v>1157086.954719</v>
+        <v>1157091.172822</v>
       </c>
       <c r="Q155" t="n">
-        <v>1307330.091229</v>
+        <v>1307335.88328</v>
       </c>
       <c r="R155" t="n">
-        <v>1462538.725233</v>
+        <v>1462546.653377</v>
       </c>
       <c r="S155" t="n">
-        <v>1628144.763024</v>
+        <v>1628155.680788</v>
       </c>
       <c r="T155" t="n">
-        <v>1800348.258395</v>
+        <v>1800363.451369</v>
       </c>
       <c r="U155" t="n">
-        <v>1977007.068121</v>
+        <v>1977028.613428</v>
       </c>
       <c r="V155" t="n">
-        <v>2157030.53467</v>
+        <v>2157062.113202</v>
       </c>
     </row>
     <row r="156">
@@ -12230,58 +12230,58 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>224917.540628</v>
+        <v>224917.54794</v>
       </c>
       <c r="F156" t="n">
-        <v>338622.87597</v>
+        <v>338622.895155</v>
       </c>
       <c r="G156" t="n">
-        <v>485836.526372</v>
+        <v>485836.561209</v>
       </c>
       <c r="H156" t="n">
-        <v>643865.585355</v>
+        <v>643865.638709</v>
       </c>
       <c r="I156" t="n">
-        <v>774427.530434</v>
+        <v>774427.600829</v>
       </c>
       <c r="J156" t="n">
-        <v>901978.706355</v>
+        <v>901978.788365</v>
       </c>
       <c r="K156" t="n">
-        <v>1014777.534357</v>
+        <v>1014777.617124</v>
       </c>
       <c r="L156" t="n">
-        <v>1105668.613293</v>
+        <v>1105668.676569</v>
       </c>
       <c r="M156" t="n">
-        <v>1187164.100296</v>
+        <v>1187164.116736</v>
       </c>
       <c r="N156" t="n">
-        <v>1254803.240551</v>
+        <v>1254803.171927</v>
       </c>
       <c r="O156" t="n">
-        <v>1293751.890452</v>
+        <v>1293751.690885</v>
       </c>
       <c r="P156" t="n">
-        <v>1321203.268986</v>
+        <v>1321202.875033</v>
       </c>
       <c r="Q156" t="n">
-        <v>1339805.669081</v>
+        <v>1339804.98863</v>
       </c>
       <c r="R156" t="n">
-        <v>1345746.193094</v>
+        <v>1345745.110039</v>
       </c>
       <c r="S156" t="n">
-        <v>1345667.180861</v>
+        <v>1345665.53576</v>
       </c>
       <c r="T156" t="n">
-        <v>1338774.385473</v>
+        <v>1338771.958529</v>
       </c>
       <c r="U156" t="n">
-        <v>1326470.320871</v>
+        <v>1326466.76728</v>
       </c>
       <c r="V156" t="n">
-        <v>1310979.549181</v>
+        <v>1310974.285357</v>
       </c>
     </row>
     <row r="157">
@@ -12306,58 +12306,58 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1421.816514</v>
+        <v>1421.815471</v>
       </c>
       <c r="F157" t="n">
-        <v>2699.505279</v>
+        <v>2699.500304</v>
       </c>
       <c r="G157" t="n">
-        <v>4721.992336</v>
+        <v>4721.976627</v>
       </c>
       <c r="H157" t="n">
-        <v>7015.187761</v>
+        <v>7015.152278</v>
       </c>
       <c r="I157" t="n">
-        <v>8833.760993</v>
+        <v>8833.699624000001</v>
       </c>
       <c r="J157" t="n">
-        <v>10311.113866</v>
+        <v>10311.020956</v>
       </c>
       <c r="K157" t="n">
-        <v>11560.348888</v>
+        <v>11560.217147</v>
       </c>
       <c r="L157" t="n">
-        <v>12666.425605</v>
+        <v>12666.244739</v>
       </c>
       <c r="M157" t="n">
-        <v>13815.993064</v>
+        <v>13815.746792</v>
       </c>
       <c r="N157" t="n">
-        <v>14857.96144</v>
+        <v>14857.632363</v>
       </c>
       <c r="O157" t="n">
-        <v>15532.80465</v>
+        <v>15532.378736</v>
       </c>
       <c r="P157" t="n">
-        <v>15993.769288</v>
+        <v>15993.22722</v>
       </c>
       <c r="Q157" t="n">
-        <v>16224.101223</v>
+        <v>16223.420788</v>
       </c>
       <c r="R157" t="n">
-        <v>16189.99607</v>
+        <v>16189.152018</v>
       </c>
       <c r="S157" t="n">
-        <v>16011.005537</v>
+        <v>16009.958734</v>
       </c>
       <c r="T157" t="n">
-        <v>15711.930138</v>
+        <v>15710.622882</v>
       </c>
       <c r="U157" t="n">
-        <v>15308.247596</v>
+        <v>15306.58923</v>
       </c>
       <c r="V157" t="n">
-        <v>14837.371402</v>
+        <v>14835.201669</v>
       </c>
     </row>
     <row r="158">
@@ -12382,58 +12382,58 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>50136.852221</v>
+        <v>50136.840329</v>
       </c>
       <c r="F158" t="n">
-        <v>66859.160685</v>
+        <v>66859.12754</v>
       </c>
       <c r="G158" t="n">
-        <v>84334.264308</v>
+        <v>84334.20069</v>
       </c>
       <c r="H158" t="n">
-        <v>101839.505406</v>
+        <v>101839.399518</v>
       </c>
       <c r="I158" t="n">
-        <v>115691.162957</v>
+        <v>115691.00311</v>
       </c>
       <c r="J158" t="n">
-        <v>130292.433415</v>
+        <v>130292.197168</v>
       </c>
       <c r="K158" t="n">
-        <v>144187.996766</v>
+        <v>144187.656345</v>
       </c>
       <c r="L158" t="n">
-        <v>155800.723743</v>
+        <v>155800.248736</v>
       </c>
       <c r="M158" t="n">
-        <v>165941.386537</v>
+        <v>165940.740944</v>
       </c>
       <c r="N158" t="n">
-        <v>173682.406826</v>
+        <v>173681.553509</v>
       </c>
       <c r="O158" t="n">
-        <v>177384.349159</v>
+        <v>177383.256212</v>
       </c>
       <c r="P158" t="n">
-        <v>179236.832125</v>
+        <v>179235.453124</v>
       </c>
       <c r="Q158" t="n">
-        <v>179234.395854</v>
+        <v>179232.675666</v>
       </c>
       <c r="R158" t="n">
-        <v>178063.074498</v>
+        <v>178060.927592</v>
       </c>
       <c r="S158" t="n">
-        <v>177299.815426</v>
+        <v>177297.094131</v>
       </c>
       <c r="T158" t="n">
-        <v>176772.695532</v>
+        <v>176769.178396</v>
       </c>
       <c r="U158" t="n">
-        <v>175851.208462</v>
+        <v>175846.563174</v>
       </c>
       <c r="V158" t="n">
-        <v>174152.8696</v>
+        <v>174146.548008</v>
       </c>
     </row>
     <row r="159">
@@ -12458,58 +12458,58 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>605.959522</v>
+        <v>605.959207</v>
       </c>
       <c r="F159" t="n">
-        <v>877.593318</v>
+        <v>877.5923320000001</v>
       </c>
       <c r="G159" t="n">
-        <v>1232.82009</v>
+        <v>1232.81786</v>
       </c>
       <c r="H159" t="n">
-        <v>1607.745798</v>
+        <v>1607.741643</v>
       </c>
       <c r="I159" t="n">
-        <v>1922.347039</v>
+        <v>1922.340327</v>
       </c>
       <c r="J159" t="n">
-        <v>2231.683941</v>
+        <v>2231.673741</v>
       </c>
       <c r="K159" t="n">
-        <v>2546.223685</v>
+        <v>2546.208637</v>
       </c>
       <c r="L159" t="n">
-        <v>2829.209692</v>
+        <v>2829.188328</v>
       </c>
       <c r="M159" t="n">
-        <v>3076.929513</v>
+        <v>3076.900246</v>
       </c>
       <c r="N159" t="n">
-        <v>3262.725843</v>
+        <v>3262.687206</v>
       </c>
       <c r="O159" t="n">
-        <v>3369.895435</v>
+        <v>3369.845937</v>
       </c>
       <c r="P159" t="n">
-        <v>3448.901913</v>
+        <v>3448.839026</v>
       </c>
       <c r="Q159" t="n">
-        <v>3485.077354</v>
+        <v>3484.998322</v>
       </c>
       <c r="R159" t="n">
-        <v>3447.703617</v>
+        <v>3447.606195</v>
       </c>
       <c r="S159" t="n">
-        <v>3354.4494</v>
+        <v>3354.330687</v>
       </c>
       <c r="T159" t="n">
-        <v>3216.111424</v>
+        <v>3215.967078</v>
       </c>
       <c r="U159" t="n">
-        <v>3056.421074</v>
+        <v>3056.243106</v>
       </c>
       <c r="V159" t="n">
-        <v>2899.598336</v>
+        <v>2899.371027</v>
       </c>
     </row>
     <row r="160">
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>13133.244107</v>
+        <v>13133.241249</v>
       </c>
       <c r="F160" t="n">
-        <v>20557.722679</v>
+        <v>20557.712661</v>
       </c>
       <c r="G160" t="n">
-        <v>31934.870504</v>
+        <v>31934.844153</v>
       </c>
       <c r="H160" t="n">
-        <v>46600.481472</v>
+        <v>46600.423526</v>
       </c>
       <c r="I160" t="n">
-        <v>61678.8375</v>
+        <v>61678.729312</v>
       </c>
       <c r="J160" t="n">
-        <v>77898.287405</v>
+        <v>77898.10359499999</v>
       </c>
       <c r="K160" t="n">
-        <v>94463.09909800001</v>
+        <v>94462.808372</v>
       </c>
       <c r="L160" t="n">
-        <v>110171.570525</v>
+        <v>110171.138116</v>
       </c>
       <c r="M160" t="n">
-        <v>126843.217167</v>
+        <v>126842.587795</v>
       </c>
       <c r="N160" t="n">
-        <v>144778.591988</v>
+        <v>144777.6845</v>
       </c>
       <c r="O160" t="n">
-        <v>162708.953167</v>
+        <v>162707.661708</v>
       </c>
       <c r="P160" t="n">
-        <v>182491.292969</v>
+        <v>182489.452775</v>
       </c>
       <c r="Q160" t="n">
-        <v>204304.865258</v>
+        <v>204302.233315</v>
       </c>
       <c r="R160" t="n">
-        <v>226924.517487</v>
+        <v>226920.76078</v>
       </c>
       <c r="S160" t="n">
-        <v>251029.195751</v>
+        <v>251023.8099</v>
       </c>
       <c r="T160" t="n">
-        <v>276555.629039</v>
+        <v>276547.831746</v>
       </c>
       <c r="U160" t="n">
-        <v>303695.993876</v>
+        <v>303684.483782</v>
       </c>
       <c r="V160" t="n">
-        <v>333091.537812</v>
+        <v>333073.941737</v>
       </c>
     </row>
     <row r="161">
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>14852.049779</v>
+        <v>14851.977172</v>
       </c>
       <c r="F162" t="n">
-        <v>12395.214399</v>
+        <v>12395.076739</v>
       </c>
       <c r="G162" t="n">
-        <v>10643.212395</v>
+        <v>10642.998107</v>
       </c>
       <c r="H162" t="n">
-        <v>10231.717941</v>
+        <v>10231.339081</v>
       </c>
       <c r="I162" t="n">
-        <v>10571.648915</v>
+        <v>10570.738937</v>
       </c>
       <c r="J162" t="n">
         <v>13516.97661</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1475.984436</v>
+        <v>1475.931181</v>
       </c>
       <c r="F163" t="n">
-        <v>2007.141377</v>
+        <v>2006.953889</v>
       </c>
       <c r="G163" t="n">
-        <v>2771.164851</v>
+        <v>2770.629544</v>
       </c>
       <c r="H163" t="n">
-        <v>3624.165061</v>
+        <v>3622.740341</v>
       </c>
       <c r="I163" t="n">
-        <v>4414.218897</v>
+        <v>4409.90113</v>
       </c>
       <c r="J163" t="n">
         <v>15766.249044</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>16376.291876</v>
+        <v>16375.964607</v>
       </c>
       <c r="F164" t="n">
-        <v>24323.450849</v>
+        <v>24322.162725</v>
       </c>
       <c r="G164" t="n">
-        <v>35682.576339</v>
+        <v>35678.598407</v>
       </c>
       <c r="H164" t="n">
-        <v>49936.010938</v>
+        <v>49924.51084</v>
       </c>
       <c r="I164" t="n">
-        <v>65150.56598</v>
+        <v>65112.688121</v>
       </c>
       <c r="J164" t="n">
         <v>181277.146596</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>57640.045392</v>
+        <v>57640.699775</v>
       </c>
       <c r="F165" t="n">
-        <v>76147.504361</v>
+        <v>76149.616777</v>
       </c>
       <c r="G165" t="n">
-        <v>89841.198902</v>
+        <v>89846.11399899999</v>
       </c>
       <c r="H165" t="n">
-        <v>106359.74092</v>
+        <v>106371.314184</v>
       </c>
       <c r="I165" t="n">
-        <v>124179.386724</v>
+        <v>124213.11054</v>
       </c>
       <c r="J165" t="n">
         <v>58405.288257</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>57207.550307</v>
+        <v>57207.342562</v>
       </c>
       <c r="F166" t="n">
-        <v>70470.681482</v>
+        <v>70469.964941</v>
       </c>
       <c r="G166" t="n">
-        <v>85369.096875</v>
+        <v>85367.20624</v>
       </c>
       <c r="H166" t="n">
-        <v>102841.783289</v>
+        <v>102837.018158</v>
       </c>
       <c r="I166" t="n">
-        <v>119210.504326</v>
+        <v>119196.564471</v>
       </c>
       <c r="J166" t="n">
         <v>168414.35841</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>530794.621868</v>
+        <v>530797.209603</v>
       </c>
       <c r="F167" t="n">
-        <v>626419.72335</v>
+        <v>626427.016509</v>
       </c>
       <c r="G167" t="n">
-        <v>744285.834372</v>
+        <v>744302.441748</v>
       </c>
       <c r="H167" t="n">
-        <v>911684.004896</v>
+        <v>911723.6199319999</v>
       </c>
       <c r="I167" t="n">
-        <v>1104493.479224</v>
+        <v>1104611.891193</v>
       </c>
       <c r="J167" t="n">
         <v>1006964.086168</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>450.414135</v>
+        <v>450.390361</v>
       </c>
       <c r="F168" t="n">
-        <v>582.959146</v>
+        <v>582.880805</v>
       </c>
       <c r="G168" t="n">
-        <v>743.0751749999999</v>
+        <v>742.872795</v>
       </c>
       <c r="H168" t="n">
-        <v>943.2035509999999</v>
+        <v>942.687536</v>
       </c>
       <c r="I168" t="n">
-        <v>1165.285924</v>
+        <v>1163.714067</v>
       </c>
       <c r="J168" t="n">
         <v>5455.325836</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>291418.61314</v>
+        <v>291418.301516</v>
       </c>
       <c r="F169" t="n">
-        <v>369000.743551</v>
+        <v>368999.465477</v>
       </c>
       <c r="G169" t="n">
-        <v>461274.039602</v>
+        <v>461270.279633</v>
       </c>
       <c r="H169" t="n">
-        <v>595678.370829</v>
+        <v>595667.699534</v>
       </c>
       <c r="I169" t="n">
-        <v>765603.748888</v>
+        <v>765567.838979</v>
       </c>
       <c r="J169" t="n">
         <v>1073732.05191</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>12670.400244</v>
+        <v>12670.134976</v>
       </c>
       <c r="F170" t="n">
-        <v>20169.748172</v>
+        <v>20168.629334</v>
       </c>
       <c r="G170" t="n">
-        <v>30057.522751</v>
+        <v>30054.046566</v>
       </c>
       <c r="H170" t="n">
-        <v>41957.009073</v>
+        <v>41947.1101</v>
       </c>
       <c r="I170" t="n">
-        <v>54531.6583</v>
+        <v>54499.560746</v>
       </c>
       <c r="J170" t="n">
         <v>152952.595242</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>67311.97526599999</v>
+        <v>67310.27374600001</v>
       </c>
       <c r="F171" t="n">
-        <v>82753.591411</v>
+        <v>82748.219866</v>
       </c>
       <c r="G171" t="n">
-        <v>100399.399085</v>
+        <v>100386.092709</v>
       </c>
       <c r="H171" t="n">
-        <v>121176.938444</v>
+        <v>121144.493177</v>
       </c>
       <c r="I171" t="n">
-        <v>141548.553136</v>
+        <v>141454.386976</v>
       </c>
       <c r="J171" t="n">
         <v>391587.860274</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>178331.418213</v>
+        <v>178328.250832</v>
       </c>
       <c r="F172" t="n">
-        <v>210651.231005</v>
+        <v>210641.662394</v>
       </c>
       <c r="G172" t="n">
-        <v>239127.007037</v>
+        <v>239105.046985</v>
       </c>
       <c r="H172" t="n">
-        <v>273928.051757</v>
+        <v>273877.735329</v>
       </c>
       <c r="I172" t="n">
-        <v>312894.787017</v>
+        <v>312752.802766</v>
       </c>
       <c r="J172" t="n">
         <v>699805.087451</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1012.766156</v>
+        <v>1012.758104</v>
       </c>
       <c r="F173" t="n">
-        <v>1532.108146</v>
+        <v>1532.074839</v>
       </c>
       <c r="G173" t="n">
-        <v>2206.232211</v>
+        <v>2206.129881</v>
       </c>
       <c r="H173" t="n">
-        <v>3020.572046</v>
+        <v>3020.28309</v>
       </c>
       <c r="I173" t="n">
-        <v>3922.158686</v>
+        <v>3921.216323</v>
       </c>
       <c r="J173" t="n">
         <v>7439.385396</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>619185.403367</v>
+        <v>619184.8557139999</v>
       </c>
       <c r="F174" t="n">
-        <v>726270.662735</v>
+        <v>726268.493431</v>
       </c>
       <c r="G174" t="n">
-        <v>846597.940347</v>
+        <v>846591.793937</v>
       </c>
       <c r="H174" t="n">
-        <v>1007403.117418</v>
+        <v>1007386.916134</v>
       </c>
       <c r="I174" t="n">
-        <v>1182716.067668</v>
+        <v>1182666.695376</v>
       </c>
       <c r="J174" t="n">
         <v>1514117.771163</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2100.869583</v>
+        <v>2100.874513</v>
       </c>
       <c r="F175" t="n">
-        <v>3742.676914</v>
+        <v>3742.69182</v>
       </c>
       <c r="G175" t="n">
-        <v>6333.671753</v>
+        <v>6333.701755</v>
       </c>
       <c r="H175" t="n">
-        <v>9991.167613</v>
+        <v>9991.220573000001</v>
       </c>
       <c r="I175" t="n">
-        <v>14640.394224</v>
+        <v>14640.495786</v>
       </c>
       <c r="J175" t="n">
         <v>20007.116002</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>178.430132</v>
+        <v>178.416347</v>
       </c>
       <c r="F176" t="n">
-        <v>198.046714</v>
+        <v>198.008381</v>
       </c>
       <c r="G176" t="n">
-        <v>229.307493</v>
+        <v>229.218469</v>
       </c>
       <c r="H176" t="n">
-        <v>279.005971</v>
+        <v>278.78958</v>
       </c>
       <c r="I176" t="n">
-        <v>343.604022</v>
+        <v>342.9499</v>
       </c>
       <c r="J176" t="n">
         <v>2105.195007</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>572454.498154</v>
+        <v>572458.001452</v>
       </c>
       <c r="F177" t="n">
-        <v>922071.3227810001</v>
+        <v>922084.057036</v>
       </c>
       <c r="G177" t="n">
-        <v>1372327.913569</v>
+        <v>1372362.465984</v>
       </c>
       <c r="H177" t="n">
-        <v>1858777.849331</v>
+        <v>1858866.39109</v>
       </c>
       <c r="I177" t="n">
-        <v>2278017.31104</v>
+        <v>2278282.447661</v>
       </c>
       <c r="J177" t="n">
         <v>1955149.950733</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>448.721979</v>
+        <v>448.691809</v>
       </c>
       <c r="F178" t="n">
-        <v>620.141848</v>
+        <v>620.035677</v>
       </c>
       <c r="G178" t="n">
-        <v>828.341099</v>
+        <v>828.054339</v>
       </c>
       <c r="H178" t="n">
-        <v>1100.582827</v>
+        <v>1099.81955</v>
       </c>
       <c r="I178" t="n">
-        <v>1423.117797</v>
+        <v>1420.694749</v>
       </c>
       <c r="J178" t="n">
         <v>8292.656112000001</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>310.045972</v>
+        <v>310.02573</v>
       </c>
       <c r="F179" t="n">
-        <v>376.928961</v>
+        <v>376.866561</v>
       </c>
       <c r="G179" t="n">
-        <v>468.921743</v>
+        <v>468.764503</v>
       </c>
       <c r="H179" t="n">
-        <v>588.299694</v>
+        <v>587.903373</v>
       </c>
       <c r="I179" t="n">
-        <v>726.773833</v>
+        <v>725.566879</v>
       </c>
       <c r="J179" t="n">
         <v>4013.214387</v>
@@ -14130,58 +14130,58 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="F181" t="n">
+        <v>-4e-06</v>
+      </c>
+      <c r="G181" t="n">
         <v>1e-06</v>
       </c>
-      <c r="F181" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G181" t="n">
-        <v>7e-06</v>
-      </c>
       <c r="H181" t="n">
-        <v>8e-06</v>
+        <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>-0</v>
+        <v>-3e-06</v>
       </c>
       <c r="J181" t="n">
         <v>2e-06</v>
       </c>
       <c r="K181" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="L181" t="n">
         <v>-1e-06</v>
       </c>
       <c r="M181" t="n">
-        <v>-2e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="N181" t="n">
         <v>-3e-06</v>
       </c>
       <c r="O181" t="n">
-        <v>7e-06</v>
+        <v>6e-06</v>
       </c>
       <c r="P181" t="n">
         <v>2e-06</v>
       </c>
       <c r="Q181" t="n">
-        <v>7e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="R181" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>5e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="T181" t="n">
-        <v>-2e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="U181" t="n">
         <v>6e-06</v>
       </c>
       <c r="V181" t="n">
-        <v>-1e-06</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
